--- a/site/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/site/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>

--- a/site/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/site/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>

--- a/site/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/site/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://www.mypalmbeachclerk.com/</t>
+          <t>https://mypalmbeachclerk.com/casesearch?caseNumber=2024-TD-004501</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-003891</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/</t>
+          <t>https://www.fultonclerk.org/case-search?docket=2024-GA-003810</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-04812</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://www.cobbtax.org/</t>
+          <t>https://www.cobbtax.org/excess-funds?docket=2024-GA-001550</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www2.miamidadeclerk.gov/ocs/Search.aspx?caseNumber=2024-CA-012874</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www.miamidadeclerk.gov/clerk/tax-deeds.page?caseNumber=2024-TD-004812</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/</t>
+          <t>https://www.fultonclerk.org/case-search?docket=2024-GA-004120</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/</t>
+          <t>https://www.hillsclerk.com/Court-Services/Tax-Deeds?caseNumber=2024-TD-008912</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www2.miamidadeclerk.gov/ocs/Search.aspx?caseNumber=2024-CA-014289</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-04950</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-004105</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>https://www.dekalbcountytax.org/</t>
+          <t>https://www.dekalbcountytax.org/excess-funds?docket=2024-GA-002490</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>https://www.mypalmbeachclerk.com/</t>
+          <t>https://mypalmbeachclerk.com/casesearch?caseNumber=2024-CA-006731</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/</t>
+          <t>https://www.dallascounty.org/government/district-clerk/tax-foreclosures.php?case=2024-TX-02044</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001955</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>https://www.mypalmbeachclerk.com/</t>
+          <t>https://mypalmbeachclerk.com/casesearch?caseNumber=2024-TD-004688</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>https://www.gwinnetttaxcommissioner.com/</t>
+          <t>https://www.gwinnetttaxcommissioner.com/excess-funds?docket=2024-GA-001920</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Web2/CaseSearch/Details/?caseNumber=2024-CA-009842</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001501</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/</t>
+          <t>https://www.dallascounty.org/government/district-clerk/tax-foreclosures.php?case=2024-TX-01928</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/</t>
+          <t>https://www.hillsclerk.com/Court-Services/Tax-Deeds?caseNumber=2024-TD-009041</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-002980</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001248</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www.miamidadeclerk.gov/clerk/tax-deeds.page?caseNumber=2024-TD-004990</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Web2/CaseSearch/Details/?caseNumber=2024-CA-011205</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-05110</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/</t>
+          <t>https://www.hillsclerk.com/Court-Services/Tax-Deeds?caseNumber=2024-TD-009188</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001622</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001844</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>

--- a/site/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/site/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://mypalmbeachclerk.com/casesearch?caseNumber=2024-TD-004501</t>
+          <t>https://www.mypalmbeachclerk.com/</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-003891</t>
+          <t>https://www.browardclerk.org/</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/case-search?docket=2024-GA-003810</t>
+          <t>https://www.fultonclerk.org/</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-04812</t>
+          <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://www.cobbtax.org/excess-funds?docket=2024-GA-001550</t>
+          <t>https://www.cobbtax.org/</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>https://www2.miamidadeclerk.gov/ocs/Search.aspx?caseNumber=2024-CA-012874</t>
+          <t>https://www.miamidadeclerk.gov/</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/clerk/tax-deeds.page?caseNumber=2024-TD-004812</t>
+          <t>https://www.miamidadeclerk.gov/</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/case-search?docket=2024-GA-004120</t>
+          <t>https://www.fultonclerk.org/</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/Court-Services/Tax-Deeds?caseNumber=2024-TD-008912</t>
+          <t>https://www.hillsclerk.com/</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>https://www2.miamidadeclerk.gov/ocs/Search.aspx?caseNumber=2024-CA-014289</t>
+          <t>https://www.miamidadeclerk.gov/</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-04950</t>
+          <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-004105</t>
+          <t>https://www.browardclerk.org/</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>https://www.dekalbcountytax.org/excess-funds?docket=2024-GA-002490</t>
+          <t>https://www.dekalbcountytax.org/</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>https://mypalmbeachclerk.com/casesearch?caseNumber=2024-CA-006731</t>
+          <t>https://www.mypalmbeachclerk.com/</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/government/district-clerk/tax-foreclosures.php?case=2024-TX-02044</t>
+          <t>https://www.dallascounty.org/</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001955</t>
+          <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>https://mypalmbeachclerk.com/casesearch?caseNumber=2024-TD-004688</t>
+          <t>https://www.mypalmbeachclerk.com/</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>https://www.gwinnetttaxcommissioner.com/excess-funds?docket=2024-GA-001920</t>
+          <t>https://www.gwinnetttaxcommissioner.com/</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/Web2/CaseSearch/Details/?caseNumber=2024-CA-009842</t>
+          <t>https://www.browardclerk.org/</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001501</t>
+          <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/government/district-clerk/tax-foreclosures.php?case=2024-TX-01928</t>
+          <t>https://www.dallascounty.org/</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/Court-Services/Tax-Deeds?caseNumber=2024-TD-009041</t>
+          <t>https://www.hillsclerk.com/</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-002980</t>
+          <t>https://www.browardclerk.org/</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001248</t>
+          <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/clerk/tax-deeds.page?caseNumber=2024-TD-004990</t>
+          <t>https://www.miamidadeclerk.gov/</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/Web2/CaseSearch/Details/?caseNumber=2024-CA-011205</t>
+          <t>https://www.browardclerk.org/</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-05110</t>
+          <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/Court-Services/Tax-Deeds?caseNumber=2024-TD-009188</t>
+          <t>https://www.hillsclerk.com/</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001622</t>
+          <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001844</t>
+          <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>

--- a/site/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/site/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://www.mypalmbeachclerk.com/</t>
+          <t>https://www.mypalmbeachclerk.com/casesearch?caseNumber=2024-TD-004501</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-003891</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/</t>
+          <t>https://www.fultonclerk.org/536/Records-Search-Center?docket=2024-GA-003810</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-04812</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://www.cobbtax.org/</t>
+          <t>https://www.cobbtax.org/property/tax_sale/index.php?docket=2024-GA-001550</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-23</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www2.miamidadeclerk.gov/QOS/default.aspx?caseNumber=2024-CA-012874</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www.miamidadeclerk.gov/clerk/property-tax-deeds.page?caseNumber=2024-TD-004812</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/</t>
+          <t>https://www.fultonclerk.org/536/Records-Search-Center?docket=2024-GA-004120</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/</t>
+          <t>https://www.hillsclerk.com/taxdeeds?caseNumber=2024-TD-008912</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-23</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www2.miamidadeclerk.gov/QOS/default.aspx?caseNumber=2024-CA-014289</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-04950</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-004105</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>https://www.dekalbcountytax.org/</t>
+          <t>https://www.dekalbcountytax.org/excess-funds?docket=2024-GA-002490</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-23</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>https://www.mypalmbeachclerk.com/</t>
+          <t>https://www.mypalmbeachclerk.com/casesearch?caseNumber=2024-CA-006731</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/</t>
+          <t>https://www.dallascounty.org/government/county-clerk/recording/foreclosures.php?case=2024-TX-02044</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myeclerk.myorangeclerk.com/?caseNumber=2024-TD-001955</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>https://www.mypalmbeachclerk.com/</t>
+          <t>https://www.mypalmbeachclerk.com/casesearch?caseNumber=2024-TD-004688</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>https://www.gwinnetttaxcommissioner.com/</t>
+          <t>https://www.gwinnetttaxcommissioner.com/property-tax/tax-sale-excess-funds?docket=2024-GA-001920</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-23</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Web2/CaseSearch/Details/?caseNumber=2024-CA-009842</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myeclerk.myorangeclerk.com/?caseNumber=2024-TD-001501</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/</t>
+          <t>https://www.dallascounty.org/government/county-clerk/recording/foreclosures.php?case=2024-TX-01928</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/</t>
+          <t>https://www.hillsclerk.com/taxdeeds?caseNumber=2024-TD-009041</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-002980</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myeclerk.myorangeclerk.com/?caseNumber=2024-TD-001248</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www.miamidadeclerk.gov/clerk/property-tax-deeds.page?caseNumber=2024-TD-004990</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-23</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Web2/CaseSearch/Details/?caseNumber=2024-CA-011205</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-05110</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/</t>
+          <t>https://www.hillsclerk.com/taxdeeds?caseNumber=2024-TD-009188</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myeclerk.myorangeclerk.com/?caseNumber=2024-TD-001622</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myeclerk.myorangeclerk.com/?caseNumber=2024-TD-001844</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>

--- a/site/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/site/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-23</t>
+          <t>2027-01-24</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2027-01-23</t>
+          <t>2027-01-24</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2027-01-23</t>
+          <t>2027-01-24</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-23</t>
+          <t>2027-01-24</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2027-01-23</t>
+          <t>2027-01-24</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>

--- a/site/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/site/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-24</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2027-01-24</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2027-01-24</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-24</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2027-01-24</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>

--- a/site/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/site/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>

--- a/site/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/site/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-26</t>
+          <t>2027-01-27</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2027-01-26</t>
+          <t>2027-01-27</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2027-01-26</t>
+          <t>2027-01-27</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-26</t>
+          <t>2027-01-27</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2027-01-26</t>
+          <t>2027-01-27</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>

--- a/site/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/site/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>

--- a/site/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/site/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>

--- a/site/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/site/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6550,7 +6550,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6682,7 +6682,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7078,7 +7078,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7592,7 +7592,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8110,7 +8110,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8238,7 +8238,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8488,7 +8488,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8620,7 +8620,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9390,7 +9390,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9512,7 +9512,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9640,7 +9640,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9762,7 +9762,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9890,7 +9890,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10018,7 +10018,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10146,7 +10146,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10396,7 +10396,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10518,7 +10518,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10890,7 +10890,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11150,7 +11150,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11278,7 +11278,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11406,7 +11406,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11534,7 +11534,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11662,7 +11662,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11912,7 +11912,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12162,7 +12162,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12284,7 +12284,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12416,7 +12416,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12548,7 +12548,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12680,7 +12680,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12802,7 +12802,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13052,7 +13052,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13180,7 +13180,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13308,7 +13308,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13436,7 +13436,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13564,7 +13564,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13692,7 +13692,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13820,7 +13820,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13948,7 +13948,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14080,7 +14080,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14202,7 +14202,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14330,7 +14330,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14452,7 +14452,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14580,7 +14580,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14840,7 +14840,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14968,7 +14968,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15096,7 +15096,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15218,7 +15218,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15350,7 +15350,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15478,7 +15478,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15606,7 +15606,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15862,7 +15862,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15990,7 +15990,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16118,7 +16118,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16250,7 +16250,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16382,7 +16382,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16510,7 +16510,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16638,7 +16638,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16770,7 +16770,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16892,7 +16892,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17020,7 +17020,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17142,7 +17142,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17270,7 +17270,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17392,7 +17392,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17514,7 +17514,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17642,7 +17642,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17764,7 +17764,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18024,7 +18024,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18152,7 +18152,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18274,7 +18274,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18402,7 +18402,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18530,7 +18530,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18658,7 +18658,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18790,7 +18790,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18918,7 +18918,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -19046,7 +19046,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -19168,7 +19168,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -19296,7 +19296,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -19424,7 +19424,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -19546,7 +19546,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -19674,7 +19674,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -19796,7 +19796,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -19918,7 +19918,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -20046,7 +20046,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -20178,7 +20178,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -20310,7 +20310,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -20442,7 +20442,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -20570,7 +20570,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -20698,7 +20698,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -20830,7 +20830,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -20952,7 +20952,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -21080,7 +21080,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -21208,7 +21208,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -21336,7 +21336,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -21468,7 +21468,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -21596,7 +21596,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -21724,7 +21724,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -21846,7 +21846,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -21974,7 +21974,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -22102,7 +22102,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -22234,7 +22234,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -22356,7 +22356,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -22484,7 +22484,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -22606,7 +22606,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -22734,7 +22734,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -22866,7 +22866,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -22988,7 +22988,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -23116,7 +23116,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -23244,7 +23244,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -23372,7 +23372,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -23500,7 +23500,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -23628,7 +23628,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -23756,7 +23756,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -23884,7 +23884,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -24006,7 +24006,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -24134,7 +24134,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -24256,7 +24256,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -24384,7 +24384,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -24512,7 +24512,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -24634,7 +24634,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -24762,7 +24762,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -24890,7 +24890,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -25018,7 +25018,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -25150,7 +25150,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -25278,7 +25278,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -25406,7 +25406,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -25534,7 +25534,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -25662,7 +25662,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -25784,7 +25784,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -25912,7 +25912,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -26044,7 +26044,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -26176,7 +26176,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -26304,7 +26304,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -26426,7 +26426,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -26548,7 +26548,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -26670,7 +26670,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -26798,7 +26798,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -26926,7 +26926,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -27182,7 +27182,7 @@
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -27314,7 +27314,7 @@
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -27436,7 +27436,7 @@
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -27568,7 +27568,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -27700,7 +27700,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -27832,7 +27832,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -27960,7 +27960,7 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -28088,7 +28088,7 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -28216,7 +28216,7 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -28344,7 +28344,7 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -28472,7 +28472,7 @@
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -28604,7 +28604,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -28726,7 +28726,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -28854,7 +28854,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -28986,7 +28986,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -29114,7 +29114,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -29242,7 +29242,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -29486,7 +29486,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -29614,7 +29614,7 @@
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -29742,7 +29742,7 @@
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -29870,7 +29870,7 @@
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -29992,7 +29992,7 @@
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -30120,7 +30120,7 @@
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -30248,7 +30248,7 @@
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -30370,7 +30370,7 @@
       </c>
       <c r="AB235" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -30492,7 +30492,7 @@
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -30614,7 +30614,7 @@
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -30736,7 +30736,7 @@
       </c>
       <c r="AB238" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -30858,7 +30858,7 @@
       </c>
       <c r="AB239" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -30986,7 +30986,7 @@
       </c>
       <c r="AB240" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AB241" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -31246,7 +31246,7 @@
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -31378,7 +31378,7 @@
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -31510,7 +31510,7 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -31632,7 +31632,7 @@
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -31754,7 +31754,7 @@
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -31882,7 +31882,7 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -32014,7 +32014,7 @@
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -32142,7 +32142,7 @@
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -32274,7 +32274,7 @@
       </c>
       <c r="AB250" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -32402,7 +32402,7 @@
       </c>
       <c r="AB251" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -32530,7 +32530,7 @@
       </c>
       <c r="AB252" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -32652,7 +32652,7 @@
       </c>
       <c r="AB253" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -32780,7 +32780,7 @@
       </c>
       <c r="AB254" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -32912,7 +32912,7 @@
       </c>
       <c r="AB255" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -33034,7 +33034,7 @@
       </c>
       <c r="AB256" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -33156,7 +33156,7 @@
       </c>
       <c r="AB257" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -33284,7 +33284,7 @@
       </c>
       <c r="AB258" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -33406,7 +33406,7 @@
       </c>
       <c r="AB259" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -33538,7 +33538,7 @@
       </c>
       <c r="AB260" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -33670,7 +33670,7 @@
       </c>
       <c r="AB261" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -33792,7 +33792,7 @@
       </c>
       <c r="AB262" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -33914,7 +33914,7 @@
       </c>
       <c r="AB263" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -34046,7 +34046,7 @@
       </c>
       <c r="AB264" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -34178,7 +34178,7 @@
       </c>
       <c r="AB265" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -34310,7 +34310,7 @@
       </c>
       <c r="AB266" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -34442,7 +34442,7 @@
       </c>
       <c r="AB267" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -34564,7 +34564,7 @@
       </c>
       <c r="AB268" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -34692,7 +34692,7 @@
       </c>
       <c r="AB269" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -34820,7 +34820,7 @@
       </c>
       <c r="AB270" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -34942,7 +34942,7 @@
       </c>
       <c r="AB271" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -35070,7 +35070,7 @@
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -35198,7 +35198,7 @@
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -35326,7 +35326,7 @@
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -35454,7 +35454,7 @@
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -35586,7 +35586,7 @@
       </c>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -35708,7 +35708,7 @@
       </c>
       <c r="AB277" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -35836,7 +35836,7 @@
       </c>
       <c r="AB278" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -35968,7 +35968,7 @@
       </c>
       <c r="AB279" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -36096,7 +36096,7 @@
       </c>
       <c r="AB280" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -36218,7 +36218,7 @@
       </c>
       <c r="AB281" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -36346,7 +36346,7 @@
       </c>
       <c r="AB282" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -36468,7 +36468,7 @@
       </c>
       <c r="AB283" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -36596,7 +36596,7 @@
       </c>
       <c r="AB284" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -36728,7 +36728,7 @@
       </c>
       <c r="AB285" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -36856,7 +36856,7 @@
       </c>
       <c r="AB286" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -36988,7 +36988,7 @@
       </c>
       <c r="AB287" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -37120,7 +37120,7 @@
       </c>
       <c r="AB288" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -37252,7 +37252,7 @@
       </c>
       <c r="AB289" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -37384,7 +37384,7 @@
       </c>
       <c r="AB290" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -37516,7 +37516,7 @@
       </c>
       <c r="AB291" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -37644,7 +37644,7 @@
       </c>
       <c r="AB292" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -37772,7 +37772,7 @@
       </c>
       <c r="AB293" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -37894,7 +37894,7 @@
       </c>
       <c r="AB294" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -38016,7 +38016,7 @@
       </c>
       <c r="AB295" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -38138,7 +38138,7 @@
       </c>
       <c r="AB296" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -38270,7 +38270,7 @@
       </c>
       <c r="AB297" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -38402,7 +38402,7 @@
       </c>
       <c r="AB298" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -38530,7 +38530,7 @@
       </c>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -38652,7 +38652,7 @@
       </c>
       <c r="AB300" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -38780,7 +38780,7 @@
       </c>
       <c r="AB301" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -38902,7 +38902,7 @@
       </c>
       <c r="AB302" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -39024,7 +39024,7 @@
       </c>
       <c r="AB303" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -39146,7 +39146,7 @@
       </c>
       <c r="AB304" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -39278,7 +39278,7 @@
       </c>
       <c r="AB305" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -39400,7 +39400,7 @@
       </c>
       <c r="AB306" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -39532,7 +39532,7 @@
       </c>
       <c r="AB307" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -39654,7 +39654,7 @@
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -39776,7 +39776,7 @@
       </c>
       <c r="AB309" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -39904,7 +39904,7 @@
       </c>
       <c r="AB310" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -40032,7 +40032,7 @@
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -40164,7 +40164,7 @@
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -40286,7 +40286,7 @@
       </c>
       <c r="AB313" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -40408,7 +40408,7 @@
       </c>
       <c r="AB314" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -40540,7 +40540,7 @@
       </c>
       <c r="AB315" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -40672,7 +40672,7 @@
       </c>
       <c r="AB316" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -40800,7 +40800,7 @@
       </c>
       <c r="AB317" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -40928,7 +40928,7 @@
       </c>
       <c r="AB318" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -41050,7 +41050,7 @@
       </c>
       <c r="AB319" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -41182,7 +41182,7 @@
       </c>
       <c r="AB320" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -41304,7 +41304,7 @@
       </c>
       <c r="AB321" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -41432,7 +41432,7 @@
       </c>
       <c r="AB322" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -41554,7 +41554,7 @@
       </c>
       <c r="AB323" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -41676,7 +41676,7 @@
       </c>
       <c r="AB324" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -41808,7 +41808,7 @@
       </c>
       <c r="AB325" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -41940,7 +41940,7 @@
       </c>
       <c r="AB326" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -42062,7 +42062,7 @@
       </c>
       <c r="AB327" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -42194,7 +42194,7 @@
       </c>
       <c r="AB328" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -42322,7 +42322,7 @@
       </c>
       <c r="AB329" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -42444,7 +42444,7 @@
       </c>
       <c r="AB330" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -42566,7 +42566,7 @@
       </c>
       <c r="AB331" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -42698,7 +42698,7 @@
       </c>
       <c r="AB332" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -42830,7 +42830,7 @@
       </c>
       <c r="AB333" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -42958,7 +42958,7 @@
       </c>
       <c r="AB334" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -43090,7 +43090,7 @@
       </c>
       <c r="AB335" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -43218,7 +43218,7 @@
       </c>
       <c r="AB336" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -43350,7 +43350,7 @@
       </c>
       <c r="AB337" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -43472,7 +43472,7 @@
       </c>
       <c r="AB338" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -43594,7 +43594,7 @@
       </c>
       <c r="AB339" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -43716,7 +43716,7 @@
       </c>
       <c r="AB340" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -43848,7 +43848,7 @@
       </c>
       <c r="AB341" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -43970,7 +43970,7 @@
       </c>
       <c r="AB342" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -44102,7 +44102,7 @@
       </c>
       <c r="AB343" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -44224,7 +44224,7 @@
       </c>
       <c r="AB344" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -44352,7 +44352,7 @@
       </c>
       <c r="AB345" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -44484,7 +44484,7 @@
       </c>
       <c r="AB346" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -44606,7 +44606,7 @@
       </c>
       <c r="AB347" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -44728,7 +44728,7 @@
       </c>
       <c r="AB348" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -44860,7 +44860,7 @@
       </c>
       <c r="AB349" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -44988,7 +44988,7 @@
       </c>
       <c r="AB350" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -45110,7 +45110,7 @@
       </c>
       <c r="AB351" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -45232,7 +45232,7 @@
       </c>
       <c r="AB352" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -45354,7 +45354,7 @@
       </c>
       <c r="AB353" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -45476,7 +45476,7 @@
       </c>
       <c r="AB354" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -45608,7 +45608,7 @@
       </c>
       <c r="AB355" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -45736,7 +45736,7 @@
       </c>
       <c r="AB356" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -45868,7 +45868,7 @@
       </c>
       <c r="AB357" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -45990,7 +45990,7 @@
       </c>
       <c r="AB358" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -46122,7 +46122,7 @@
       </c>
       <c r="AB359" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -46254,7 +46254,7 @@
       </c>
       <c r="AB360" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -46376,7 +46376,7 @@
       </c>
       <c r="AB361" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -46504,7 +46504,7 @@
       </c>
       <c r="AB362" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -46632,7 +46632,7 @@
       </c>
       <c r="AB363" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -46760,7 +46760,7 @@
       </c>
       <c r="AB364" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -46882,7 +46882,7 @@
       </c>
       <c r="AB365" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -47010,7 +47010,7 @@
       </c>
       <c r="AB366" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -47132,7 +47132,7 @@
       </c>
       <c r="AB367" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -47260,7 +47260,7 @@
       </c>
       <c r="AB368" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -47382,7 +47382,7 @@
       </c>
       <c r="AB369" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -47514,7 +47514,7 @@
       </c>
       <c r="AB370" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -47636,7 +47636,7 @@
       </c>
       <c r="AB371" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -47764,7 +47764,7 @@
       </c>
       <c r="AB372" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -47896,7 +47896,7 @@
       </c>
       <c r="AB373" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -48028,7 +48028,7 @@
       </c>
       <c r="AB374" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -48156,7 +48156,7 @@
       </c>
       <c r="AB375" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -48288,7 +48288,7 @@
       </c>
       <c r="AB376" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -48420,7 +48420,7 @@
       </c>
       <c r="AB377" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -48548,7 +48548,7 @@
       </c>
       <c r="AB378" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -48670,7 +48670,7 @@
       </c>
       <c r="AB379" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -48792,7 +48792,7 @@
       </c>
       <c r="AB380" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -48924,7 +48924,7 @@
       </c>
       <c r="AB381" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -49056,7 +49056,7 @@
       </c>
       <c r="AB382" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -49188,7 +49188,7 @@
       </c>
       <c r="AB383" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -49310,7 +49310,7 @@
       </c>
       <c r="AB384" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -49442,7 +49442,7 @@
       </c>
       <c r="AB385" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -49570,7 +49570,7 @@
       </c>
       <c r="AB386" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -49702,7 +49702,7 @@
       </c>
       <c r="AB387" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -49824,7 +49824,7 @@
       </c>
       <c r="AB388" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -49956,7 +49956,7 @@
       </c>
       <c r="AB389" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -50084,7 +50084,7 @@
       </c>
       <c r="AB390" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -50206,7 +50206,7 @@
       </c>
       <c r="AB391" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -50334,7 +50334,7 @@
       </c>
       <c r="AB392" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -50456,7 +50456,7 @@
       </c>
       <c r="AB393" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -50584,7 +50584,7 @@
       </c>
       <c r="AB394" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -50712,7 +50712,7 @@
       </c>
       <c r="AB395" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -50834,7 +50834,7 @@
       </c>
       <c r="AB396" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -50956,7 +50956,7 @@
       </c>
       <c r="AB397" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -51078,7 +51078,7 @@
       </c>
       <c r="AB398" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -51200,7 +51200,7 @@
       </c>
       <c r="AB399" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -51322,7 +51322,7 @@
       </c>
       <c r="AB400" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -51444,7 +51444,7 @@
       </c>
       <c r="AB401" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -51572,7 +51572,7 @@
       </c>
       <c r="AB402" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -51700,7 +51700,7 @@
       </c>
       <c r="AB403" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -51832,7 +51832,7 @@
       </c>
       <c r="AB404" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -51964,7 +51964,7 @@
       </c>
       <c r="AB405" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -52086,7 +52086,7 @@
       </c>
       <c r="AB406" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -52208,7 +52208,7 @@
       </c>
       <c r="AB407" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -52340,7 +52340,7 @@
       </c>
       <c r="AB408" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -52472,7 +52472,7 @@
       </c>
       <c r="AB409" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -52594,7 +52594,7 @@
       </c>
       <c r="AB410" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -52722,7 +52722,7 @@
       </c>
       <c r="AB411" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -52854,7 +52854,7 @@
       </c>
       <c r="AB412" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -52986,7 +52986,7 @@
       </c>
       <c r="AB413" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -53108,7 +53108,7 @@
       </c>
       <c r="AB414" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -53236,7 +53236,7 @@
       </c>
       <c r="AB415" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -53368,7 +53368,7 @@
       </c>
       <c r="AB416" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -53500,7 +53500,7 @@
       </c>
       <c r="AB417" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -53632,7 +53632,7 @@
       </c>
       <c r="AB418" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -53754,7 +53754,7 @@
       </c>
       <c r="AB419" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -53886,7 +53886,7 @@
       </c>
       <c r="AB420" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -54008,7 +54008,7 @@
       </c>
       <c r="AB421" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -54130,7 +54130,7 @@
       </c>
       <c r="AB422" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -54252,7 +54252,7 @@
       </c>
       <c r="AB423" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -54374,7 +54374,7 @@
       </c>
       <c r="AB424" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -54496,7 +54496,7 @@
       </c>
       <c r="AB425" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -54628,7 +54628,7 @@
       </c>
       <c r="AB426" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -54760,7 +54760,7 @@
       </c>
       <c r="AB427" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -54882,7 +54882,7 @@
       </c>
       <c r="AB428" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -55004,7 +55004,7 @@
       </c>
       <c r="AB429" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -55126,7 +55126,7 @@
       </c>
       <c r="AB430" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -55248,7 +55248,7 @@
       </c>
       <c r="AB431" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -55380,7 +55380,7 @@
       </c>
       <c r="AB432" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -55512,7 +55512,7 @@
       </c>
       <c r="AB433" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -55644,7 +55644,7 @@
       </c>
       <c r="AB434" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -55766,7 +55766,7 @@
       </c>
       <c r="AB435" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -55888,7 +55888,7 @@
       </c>
       <c r="AB436" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -56020,7 +56020,7 @@
       </c>
       <c r="AB437" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -56152,7 +56152,7 @@
       </c>
       <c r="AB438" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -56274,7 +56274,7 @@
       </c>
       <c r="AB439" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -56406,7 +56406,7 @@
       </c>
       <c r="AB440" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -56528,7 +56528,7 @@
       </c>
       <c r="AB441" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -56650,7 +56650,7 @@
       </c>
       <c r="AB442" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -56778,7 +56778,7 @@
       </c>
       <c r="AB443" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -56900,7 +56900,7 @@
       </c>
       <c r="AB444" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -57022,7 +57022,7 @@
       </c>
       <c r="AB445" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -57154,7 +57154,7 @@
       </c>
       <c r="AB446" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -57276,7 +57276,7 @@
       </c>
       <c r="AB447" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -57398,7 +57398,7 @@
       </c>
       <c r="AB448" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -57520,7 +57520,7 @@
       </c>
       <c r="AB449" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -57642,7 +57642,7 @@
       </c>
       <c r="AB450" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -57764,7 +57764,7 @@
       </c>
       <c r="AB451" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -57896,7 +57896,7 @@
       </c>
       <c r="AB452" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -58018,7 +58018,7 @@
       </c>
       <c r="AB453" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -58140,7 +58140,7 @@
       </c>
       <c r="AB454" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -58268,7 +58268,7 @@
       </c>
       <c r="AB455" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -58396,7 +58396,7 @@
       </c>
       <c r="AB456" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -58518,7 +58518,7 @@
       </c>
       <c r="AB457" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -58650,7 +58650,7 @@
       </c>
       <c r="AB458" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -58772,7 +58772,7 @@
       </c>
       <c r="AB459" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -58894,7 +58894,7 @@
       </c>
       <c r="AB460" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -59016,7 +59016,7 @@
       </c>
       <c r="AB461" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -59144,7 +59144,7 @@
       </c>
       <c r="AB462" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -59272,7 +59272,7 @@
       </c>
       <c r="AB463" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -59400,7 +59400,7 @@
       </c>
       <c r="AB464" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -59522,7 +59522,7 @@
       </c>
       <c r="AB465" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -59650,7 +59650,7 @@
       </c>
       <c r="AB466" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -59778,7 +59778,7 @@
       </c>
       <c r="AB467" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -59900,7 +59900,7 @@
       </c>
       <c r="AB468" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -60028,7 +60028,7 @@
       </c>
       <c r="AB469" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -60150,7 +60150,7 @@
       </c>
       <c r="AB470" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>

--- a/site/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/site/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -855,12 +855,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>P. &amp; B. K████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>P. &amp; B. A██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -999,17 +999,17 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>P. &amp; B. K████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>P. &amp; B. A██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1575,12 +1575,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1727,12 +1727,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1869,12 +1869,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=23-CA-016325</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=23-CA-016325</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -2007,12 +2007,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -2155,12 +2155,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-88</v>
+        <v>-89</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2307,12 +2307,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>K. &amp; A. H███████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>L. &amp; L. A██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2455,17 +2455,17 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>K. &amp; A. H███████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>L. &amp; L. A██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2603,12 +2603,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2755,12 +2755,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2907,12 +2907,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Y. &amp; M. L████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>R. &amp; V. W██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -3055,17 +3055,17 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Y. &amp; M. L████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>R. &amp; V. W██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -3203,12 +3203,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3493,12 +3493,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3635,12 +3635,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P25" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4305,7 +4305,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>-88</v>
+        <v>-89</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4359,12 +4359,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P28" t="n">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4655,12 +4655,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4807,12 +4807,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4905,7 +4905,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4959,12 +4959,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -5111,12 +5111,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -5209,7 +5209,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -5263,12 +5263,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P34" t="inlineStr"/>
@@ -5370,7 +5370,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=26-CA-006185</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=26-CA-006185</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -5405,12 +5405,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5647,7 +5647,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5701,12 +5701,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -5929,7 +5929,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -6077,7 +6077,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -6131,12 +6131,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -6229,7 +6229,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -6283,12 +6283,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -6435,12 +6435,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -6533,7 +6533,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -6587,12 +6587,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -6739,12 +6739,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -6881,12 +6881,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -7029,12 +7029,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -7127,7 +7127,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -7181,12 +7181,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>A. &amp; F. F██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>P. &amp; B. H███████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -7329,17 +7329,17 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>A. &amp; F. F██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>P. &amp; B. H███████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
@@ -7423,7 +7423,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -7477,12 +7477,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -7713,7 +7713,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -7767,12 +7767,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -7865,7 +7865,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -7919,12 +7919,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -8067,12 +8067,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P53" t="inlineStr"/>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=24-CA-001841</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=24-CA-001841</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -8349,12 +8349,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -8443,7 +8443,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -8639,12 +8639,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -8733,7 +8733,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -8787,12 +8787,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -8881,7 +8881,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -8935,12 +8935,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -9021,7 +9021,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -9169,7 +9169,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -9223,12 +9223,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -9317,7 +9317,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -9371,12 +9371,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -9513,12 +9513,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -9603,7 +9603,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -9657,12 +9657,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>J. &amp; C. J████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>G. &amp; C. T█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -9894,7 +9894,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -9939,17 +9939,17 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>J. &amp; C. J████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>G. &amp; C. T█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
@@ -10029,7 +10029,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -10083,12 +10083,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -10173,7 +10173,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -10227,12 +10227,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P68" t="n">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -10509,12 +10509,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -10599,7 +10599,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -10653,12 +10653,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
@@ -10791,12 +10791,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -10929,12 +10929,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
@@ -11015,7 +11015,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P73" t="n">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -11073,12 +11073,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -11167,7 +11167,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -11221,12 +11221,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
@@ -11315,7 +11315,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -11369,12 +11369,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
@@ -11413,7 +11413,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>A. &amp; E. P████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>R. &amp; D. P████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -11455,7 +11455,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P76" t="n">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -11513,17 +11513,17 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>A. &amp; E. P████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>R. &amp; D. P████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD76" t="inlineStr">
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -11657,12 +11657,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
@@ -11747,7 +11747,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -11801,12 +11801,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
@@ -11887,7 +11887,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P79" t="n">
@@ -11900,7 +11900,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -11945,12 +11945,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
@@ -12173,7 +12173,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -12227,12 +12227,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
@@ -12365,12 +12365,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
@@ -12459,7 +12459,7 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -12513,12 +12513,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -12611,7 +12611,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
@@ -12763,7 +12763,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -12817,12 +12817,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
@@ -12959,12 +12959,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
@@ -13097,12 +13097,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
@@ -13187,7 +13187,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -13241,12 +13241,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
@@ -13331,7 +13331,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -13385,12 +13385,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -13475,7 +13475,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -13529,12 +13529,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -13615,7 +13615,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P91" t="n">
@@ -13628,7 +13628,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -13673,12 +13673,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
@@ -13717,7 +13717,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>L. &amp; G. P████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>M. &amp; S. P████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -13759,7 +13759,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P92" t="n">
@@ -13772,7 +13772,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -13817,17 +13817,17 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>L. &amp; G. P████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>M. &amp; S. P████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD92" t="inlineStr">
@@ -13907,7 +13907,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -13961,12 +13961,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
@@ -14051,7 +14051,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -14105,12 +14105,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
@@ -14195,7 +14195,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -14249,12 +14249,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
@@ -14343,7 +14343,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -14397,12 +14397,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
@@ -14487,7 +14487,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P97" t="inlineStr"/>
@@ -14504,7 +14504,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=23-CA-017541</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=23-CA-017541</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -14514,7 +14514,7 @@
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
@@ -14539,12 +14539,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
@@ -14625,7 +14625,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P98" t="n">
@@ -14638,7 +14638,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
@@ -14773,7 +14773,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -14827,12 +14827,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
@@ -14921,7 +14921,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -14975,12 +14975,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
@@ -15069,7 +15069,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -15123,12 +15123,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
@@ -15213,7 +15213,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -15267,12 +15267,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
@@ -15357,7 +15357,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -15411,12 +15411,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
@@ -15497,7 +15497,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P104" t="inlineStr"/>
@@ -15514,7 +15514,7 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=21-CA-005559</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=21-CA-005559</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
@@ -15524,7 +15524,7 @@
       </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W104" t="inlineStr">
@@ -15549,12 +15549,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
@@ -15643,7 +15643,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -15697,12 +15697,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
@@ -15791,7 +15791,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -15845,12 +15845,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
@@ -15935,7 +15935,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -15989,12 +15989,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
@@ -16075,7 +16075,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -16088,7 +16088,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
@@ -16133,12 +16133,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
@@ -16219,7 +16219,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -16232,7 +16232,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
@@ -16277,12 +16277,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
@@ -16367,7 +16367,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -16421,12 +16421,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
@@ -16511,7 +16511,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -16565,12 +16565,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
@@ -16659,7 +16659,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -16713,12 +16713,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
@@ -16811,7 +16811,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -16865,12 +16865,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
@@ -16959,7 +16959,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -17013,12 +17013,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
@@ -17099,7 +17099,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -17112,7 +17112,7 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
@@ -17157,12 +17157,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
@@ -17251,7 +17251,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -17305,12 +17305,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
@@ -17447,12 +17447,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
@@ -17541,7 +17541,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -17595,12 +17595,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
@@ -17685,7 +17685,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -17739,12 +17739,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
@@ -17877,12 +17877,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
@@ -17967,7 +17967,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -18021,12 +18021,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
@@ -18159,12 +18159,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
@@ -18297,12 +18297,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
@@ -18387,7 +18387,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -18441,12 +18441,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
@@ -18535,7 +18535,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -18589,12 +18589,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
@@ -18679,7 +18679,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P126" t="n">
@@ -18692,7 +18692,7 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
@@ -18737,12 +18737,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr">
@@ -18875,12 +18875,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr">
@@ -18965,7 +18965,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P128" t="n">
@@ -18978,7 +18978,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
@@ -19023,12 +19023,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr">
@@ -19113,7 +19113,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -19167,12 +19167,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr">
@@ -19257,7 +19257,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -19311,12 +19311,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr">
@@ -19405,7 +19405,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -19459,12 +19459,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr">
@@ -19549,7 +19549,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P132" t="n">
@@ -19562,7 +19562,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
@@ -19607,12 +19607,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr">
@@ -19697,7 +19697,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -19751,12 +19751,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
@@ -19889,12 +19889,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
@@ -19979,7 +19979,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -20033,12 +20033,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC135" t="inlineStr">
@@ -20119,7 +20119,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P136" t="n">
@@ -20132,7 +20132,7 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S136" t="inlineStr">
@@ -20177,12 +20177,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr">
@@ -20315,12 +20315,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr">
@@ -20405,7 +20405,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -20459,12 +20459,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr">
@@ -20545,7 +20545,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P139" t="inlineStr"/>
@@ -20562,7 +20562,7 @@
       </c>
       <c r="T139" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=21-CA-004936</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=21-CA-004936</t>
         </is>
       </c>
       <c r="U139" t="inlineStr">
@@ -20572,7 +20572,7 @@
       </c>
       <c r="V139" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W139" t="inlineStr">
@@ -20597,12 +20597,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr">
@@ -20735,12 +20735,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
@@ -20825,7 +20825,7 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
@@ -20879,12 +20879,12 @@
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC141" t="inlineStr">
@@ -20973,7 +20973,7 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
@@ -21027,12 +21027,12 @@
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC142" t="inlineStr">
@@ -21125,7 +21125,7 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
@@ -21179,12 +21179,12 @@
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC143" t="inlineStr">
@@ -21277,7 +21277,7 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
@@ -21331,12 +21331,12 @@
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC144" t="inlineStr">
@@ -21425,7 +21425,7 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
@@ -21479,12 +21479,12 @@
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC145" t="inlineStr">
@@ -21565,7 +21565,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P146" t="n">
@@ -21578,7 +21578,7 @@
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S146" t="inlineStr">
@@ -21623,12 +21623,12 @@
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC146" t="inlineStr">
@@ -21717,7 +21717,7 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
@@ -21771,12 +21771,12 @@
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC147" t="inlineStr">
@@ -21865,7 +21865,7 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
@@ -21919,12 +21919,12 @@
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC148" t="inlineStr">
@@ -22005,7 +22005,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P149" t="n">
@@ -22018,7 +22018,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S149" t="inlineStr">
@@ -22063,12 +22063,12 @@
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC149" t="inlineStr">
@@ -22153,7 +22153,7 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
@@ -22207,12 +22207,12 @@
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC150" t="inlineStr">
@@ -22301,7 +22301,7 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
@@ -22355,12 +22355,12 @@
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC151" t="inlineStr">
@@ -22445,7 +22445,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P152" t="n">
@@ -22458,7 +22458,7 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S152" t="inlineStr">
@@ -22503,12 +22503,12 @@
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC152" t="inlineStr">
@@ -22593,7 +22593,7 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
@@ -22647,12 +22647,12 @@
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC153" t="inlineStr">
@@ -22737,7 +22737,7 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
@@ -22791,12 +22791,12 @@
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC154" t="inlineStr">
@@ -22881,7 +22881,7 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
@@ -22935,12 +22935,12 @@
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC155" t="inlineStr">
@@ -23029,7 +23029,7 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
@@ -23083,12 +23083,12 @@
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC156" t="inlineStr">
@@ -23173,7 +23173,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P157" t="inlineStr"/>
@@ -23190,7 +23190,7 @@
       </c>
       <c r="T157" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=23-CA-014882</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=23-CA-014882</t>
         </is>
       </c>
       <c r="U157" t="inlineStr">
@@ -23200,7 +23200,7 @@
       </c>
       <c r="V157" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
@@ -23225,12 +23225,12 @@
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC157" t="inlineStr">
@@ -23315,7 +23315,7 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
@@ -23369,12 +23369,12 @@
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC158" t="inlineStr">
@@ -23455,7 +23455,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P159" t="n">
@@ -23468,7 +23468,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S159" t="inlineStr">
@@ -23513,12 +23513,12 @@
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC159" t="inlineStr">
@@ -23607,7 +23607,7 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>-88</v>
+        <v>-89</v>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
@@ -23661,12 +23661,12 @@
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC160" t="inlineStr">
@@ -23803,12 +23803,12 @@
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC161" t="inlineStr">
@@ -23889,7 +23889,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P162" t="n">
@@ -23902,7 +23902,7 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S162" t="inlineStr">
@@ -23947,12 +23947,12 @@
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC162" t="inlineStr">
@@ -24037,7 +24037,7 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
@@ -24091,12 +24091,12 @@
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC163" t="inlineStr">
@@ -24181,7 +24181,7 @@
         </is>
       </c>
       <c r="P164" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
@@ -24235,12 +24235,12 @@
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC164" t="inlineStr">
@@ -24325,7 +24325,7 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
@@ -24379,12 +24379,12 @@
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC165" t="inlineStr">
@@ -24469,7 +24469,7 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
@@ -24523,12 +24523,12 @@
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC166" t="inlineStr">
@@ -24613,7 +24613,7 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
@@ -24667,12 +24667,12 @@
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC167" t="inlineStr">
@@ -24757,7 +24757,7 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
@@ -24811,12 +24811,12 @@
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC168" t="inlineStr">
@@ -24949,12 +24949,12 @@
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC169" t="inlineStr">
@@ -25035,7 +25035,7 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P170" t="n">
@@ -25048,7 +25048,7 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S170" t="inlineStr">
@@ -25093,12 +25093,12 @@
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC170" t="inlineStr">
@@ -25231,12 +25231,12 @@
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC171" t="inlineStr">
@@ -25321,7 +25321,7 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="Q172" t="inlineStr">
         <is>
@@ -25375,12 +25375,12 @@
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC172" t="inlineStr">
@@ -25461,7 +25461,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P173" t="n">
@@ -25474,7 +25474,7 @@
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S173" t="inlineStr">
@@ -25519,12 +25519,12 @@
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC173" t="inlineStr">
@@ -25609,7 +25609,7 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q174" t="inlineStr">
         <is>
@@ -25663,12 +25663,12 @@
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC174" t="inlineStr">
@@ -25749,7 +25749,7 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P175" t="n">
@@ -25762,7 +25762,7 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S175" t="inlineStr">
@@ -25807,12 +25807,12 @@
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC175" t="inlineStr">
@@ -25893,7 +25893,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P176" t="n">
@@ -25906,7 +25906,7 @@
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S176" t="inlineStr">
@@ -25951,12 +25951,12 @@
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC176" t="inlineStr">
@@ -26089,12 +26089,12 @@
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC177" t="inlineStr">
@@ -26183,7 +26183,7 @@
         </is>
       </c>
       <c r="P178" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Q178" t="inlineStr">
         <is>
@@ -26237,12 +26237,12 @@
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC178" t="inlineStr">
@@ -26327,7 +26327,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P179" t="n">
@@ -26340,7 +26340,7 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S179" t="inlineStr">
@@ -26385,12 +26385,12 @@
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC179" t="inlineStr">
@@ -26475,7 +26475,7 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q180" t="inlineStr">
         <is>
@@ -26529,12 +26529,12 @@
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC180" t="inlineStr">
@@ -26615,7 +26615,7 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P181" t="n">
@@ -26628,7 +26628,7 @@
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S181" t="inlineStr">
@@ -26673,12 +26673,12 @@
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC181" t="inlineStr">
@@ -26717,7 +26717,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>R. &amp; D. T█████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>D. &amp; W. H█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -26759,7 +26759,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P182" t="n">
@@ -26772,7 +26772,7 @@
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S182" t="inlineStr">
@@ -26817,17 +26817,17 @@
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>R. &amp; D. T█████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>D. &amp; W. H█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD182" t="inlineStr">
@@ -26955,12 +26955,12 @@
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC183" t="inlineStr">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P184" t="n">
@@ -27054,7 +27054,7 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S184" t="inlineStr">
@@ -27099,12 +27099,12 @@
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC184" t="inlineStr">
@@ -27193,7 +27193,7 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
@@ -27247,12 +27247,12 @@
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC185" t="inlineStr">
@@ -27345,7 +27345,7 @@
         </is>
       </c>
       <c r="P186" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
@@ -27399,12 +27399,12 @@
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC186" t="inlineStr">
@@ -27489,7 +27489,7 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P187" t="n">
@@ -27502,7 +27502,7 @@
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S187" t="inlineStr">
@@ -27547,12 +27547,12 @@
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC187" t="inlineStr">
@@ -27633,7 +27633,7 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P188" t="inlineStr"/>
@@ -27650,7 +27650,7 @@
       </c>
       <c r="T188" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=26-CA-000549</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=26-CA-000549</t>
         </is>
       </c>
       <c r="U188" t="inlineStr">
@@ -27660,7 +27660,7 @@
       </c>
       <c r="V188" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W188" t="inlineStr">
@@ -27685,12 +27685,12 @@
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC188" t="inlineStr">
@@ -27823,12 +27823,12 @@
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC189" t="inlineStr">
@@ -27913,7 +27913,7 @@
         </is>
       </c>
       <c r="P190" t="n">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="Q190" t="inlineStr">
         <is>
@@ -27967,12 +27967,12 @@
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC190" t="inlineStr">
@@ -28057,7 +28057,7 @@
         </is>
       </c>
       <c r="P191" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q191" t="inlineStr">
         <is>
@@ -28111,12 +28111,12 @@
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC191" t="inlineStr">
@@ -28201,7 +28201,7 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
@@ -28255,12 +28255,12 @@
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC192" t="inlineStr">
@@ -28345,7 +28345,7 @@
         </is>
       </c>
       <c r="P193" t="n">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
@@ -28399,12 +28399,12 @@
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC193" t="inlineStr">
@@ -28493,7 +28493,7 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="Q194" t="inlineStr">
         <is>
@@ -28547,12 +28547,12 @@
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC194" t="inlineStr">
@@ -28645,7 +28645,7 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
@@ -28699,12 +28699,12 @@
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC195" t="inlineStr">
@@ -28797,7 +28797,7 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
@@ -28851,12 +28851,12 @@
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC196" t="inlineStr">
@@ -28949,7 +28949,7 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="Q197" t="inlineStr">
         <is>
@@ -29003,12 +29003,12 @@
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC197" t="inlineStr">
@@ -29093,7 +29093,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P198" t="n">
@@ -29106,7 +29106,7 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S198" t="inlineStr">
@@ -29151,12 +29151,12 @@
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC198" t="inlineStr">
@@ -29195,7 +29195,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>S. &amp; W. W████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>J. &amp; L. A███████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -29237,7 +29237,7 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P199" t="n">
@@ -29250,7 +29250,7 @@
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S199" t="inlineStr">
@@ -29295,17 +29295,17 @@
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC199" t="inlineStr">
         <is>
-          <t>S. &amp; W. W████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>J. &amp; L. A███████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD199" t="inlineStr">
@@ -29381,7 +29381,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P200" t="n">
@@ -29394,7 +29394,7 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S200" t="inlineStr">
@@ -29439,12 +29439,12 @@
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC200" t="inlineStr">
@@ -29529,7 +29529,7 @@
         </is>
       </c>
       <c r="P201" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q201" t="inlineStr">
         <is>
@@ -29583,12 +29583,12 @@
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC201" t="inlineStr">
@@ -29669,7 +29669,7 @@
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P202" t="n">
@@ -29682,7 +29682,7 @@
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S202" t="inlineStr">
@@ -29727,12 +29727,12 @@
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC202" t="inlineStr">
@@ -29821,7 +29821,7 @@
         </is>
       </c>
       <c r="P203" t="n">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="Q203" t="inlineStr">
         <is>
@@ -29875,12 +29875,12 @@
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC203" t="inlineStr">
@@ -29969,7 +29969,7 @@
         </is>
       </c>
       <c r="P204" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q204" t="inlineStr">
         <is>
@@ -30023,12 +30023,12 @@
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC204" t="inlineStr">
@@ -30117,7 +30117,7 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="Q205" t="inlineStr">
         <is>
@@ -30171,12 +30171,12 @@
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC205" t="inlineStr">
@@ -30265,7 +30265,7 @@
         </is>
       </c>
       <c r="P206" t="n">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="Q206" t="inlineStr">
         <is>
@@ -30319,12 +30319,12 @@
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC206" t="inlineStr">
@@ -30405,7 +30405,7 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P207" t="n">
@@ -30418,7 +30418,7 @@
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S207" t="inlineStr">
@@ -30463,12 +30463,12 @@
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC207" t="inlineStr">
@@ -30549,7 +30549,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P208" t="inlineStr"/>
@@ -30566,7 +30566,7 @@
       </c>
       <c r="T208" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=25-CA-002135</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=25-CA-002135</t>
         </is>
       </c>
       <c r="U208" t="inlineStr">
@@ -30576,7 +30576,7 @@
       </c>
       <c r="V208" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W208" t="inlineStr">
@@ -30601,12 +30601,12 @@
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC208" t="inlineStr">
@@ -30687,7 +30687,7 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P209" t="inlineStr"/>
@@ -30704,7 +30704,7 @@
       </c>
       <c r="T209" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=22-CA-008602</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=22-CA-008602</t>
         </is>
       </c>
       <c r="U209" t="inlineStr">
@@ -30714,7 +30714,7 @@
       </c>
       <c r="V209" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W209" t="inlineStr">
@@ -30739,12 +30739,12 @@
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC209" t="inlineStr">
@@ -30825,7 +30825,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P210" t="n">
@@ -30838,7 +30838,7 @@
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S210" t="inlineStr">
@@ -30883,12 +30883,12 @@
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC210" t="inlineStr">
@@ -30973,7 +30973,7 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q211" t="inlineStr">
         <is>
@@ -31027,12 +31027,12 @@
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC211" t="inlineStr">
@@ -31113,7 +31113,7 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P212" t="n">
@@ -31126,7 +31126,7 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S212" t="inlineStr">
@@ -31171,12 +31171,12 @@
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC212" t="inlineStr">
@@ -31257,7 +31257,7 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P213" t="n">
@@ -31270,7 +31270,7 @@
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S213" t="inlineStr">
@@ -31315,12 +31315,12 @@
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC213" t="inlineStr">
@@ -31405,7 +31405,7 @@
         </is>
       </c>
       <c r="P214" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q214" t="inlineStr">
         <is>
@@ -31459,12 +31459,12 @@
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC214" t="inlineStr">
@@ -31597,12 +31597,12 @@
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC215" t="inlineStr">
@@ -31683,7 +31683,7 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P216" t="n">
@@ -31696,7 +31696,7 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S216" t="inlineStr">
@@ -31741,12 +31741,12 @@
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC216" t="inlineStr">
@@ -31827,7 +31827,7 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P217" t="n">
@@ -31840,7 +31840,7 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S217" t="inlineStr">
@@ -31885,12 +31885,12 @@
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC217" t="inlineStr">
@@ -31979,7 +31979,7 @@
         </is>
       </c>
       <c r="P218" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q218" t="inlineStr">
         <is>
@@ -32033,12 +32033,12 @@
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC218" t="inlineStr">
@@ -32131,7 +32131,7 @@
         </is>
       </c>
       <c r="P219" t="n">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Q219" t="inlineStr">
         <is>
@@ -32185,12 +32185,12 @@
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC219" t="inlineStr">
@@ -32283,7 +32283,7 @@
         </is>
       </c>
       <c r="P220" t="n">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="Q220" t="inlineStr">
         <is>
@@ -32337,12 +32337,12 @@
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC220" t="inlineStr">
@@ -32479,12 +32479,12 @@
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC221" t="inlineStr">
@@ -32569,7 +32569,7 @@
         </is>
       </c>
       <c r="P222" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q222" t="inlineStr">
         <is>
@@ -32623,12 +32623,12 @@
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC222" t="inlineStr">
@@ -32717,7 +32717,7 @@
         </is>
       </c>
       <c r="P223" t="n">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="Q223" t="inlineStr">
         <is>
@@ -32771,12 +32771,12 @@
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC223" t="inlineStr">
@@ -32865,7 +32865,7 @@
         </is>
       </c>
       <c r="P224" t="n">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="Q224" t="inlineStr">
         <is>
@@ -32919,12 +32919,12 @@
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC224" t="inlineStr">
@@ -33013,7 +33013,7 @@
         </is>
       </c>
       <c r="P225" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q225" t="inlineStr">
         <is>
@@ -33067,12 +33067,12 @@
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC225" t="inlineStr">
@@ -33161,7 +33161,7 @@
         </is>
       </c>
       <c r="P226" t="n">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="Q226" t="inlineStr">
         <is>
@@ -33215,12 +33215,12 @@
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC226" t="inlineStr">
@@ -33305,7 +33305,7 @@
         </is>
       </c>
       <c r="P227" t="n">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="Q227" t="inlineStr">
         <is>
@@ -33359,12 +33359,12 @@
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC227" t="inlineStr">
@@ -33497,12 +33497,12 @@
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC228" t="inlineStr">
@@ -33587,7 +33587,7 @@
         </is>
       </c>
       <c r="P229" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q229" t="inlineStr">
         <is>
@@ -33641,12 +33641,12 @@
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC229" t="inlineStr">
@@ -33735,7 +33735,7 @@
         </is>
       </c>
       <c r="P230" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q230" t="inlineStr">
         <is>
@@ -33789,12 +33789,12 @@
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC230" t="inlineStr">
@@ -33879,7 +33879,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P231" t="n">
@@ -33892,7 +33892,7 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S231" t="inlineStr">
@@ -33937,12 +33937,12 @@
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC231" t="inlineStr">
@@ -34031,7 +34031,7 @@
         </is>
       </c>
       <c r="P232" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q232" t="inlineStr">
         <is>
@@ -34085,12 +34085,12 @@
       </c>
       <c r="AA232" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC232" t="inlineStr">
@@ -34183,7 +34183,7 @@
         </is>
       </c>
       <c r="P233" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q233" t="inlineStr">
         <is>
@@ -34237,12 +34237,12 @@
       </c>
       <c r="AA233" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC233" t="inlineStr">
@@ -34379,12 +34379,12 @@
       </c>
       <c r="AA234" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC234" t="inlineStr">
@@ -34465,7 +34465,7 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P235" t="inlineStr"/>
@@ -34482,7 +34482,7 @@
       </c>
       <c r="T235" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=26-CA-007844</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=26-CA-007844</t>
         </is>
       </c>
       <c r="U235" t="inlineStr">
@@ -34492,7 +34492,7 @@
       </c>
       <c r="V235" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W235" t="inlineStr">
@@ -34517,12 +34517,12 @@
       </c>
       <c r="AA235" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB235" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC235" t="inlineStr">
@@ -34611,7 +34611,7 @@
         </is>
       </c>
       <c r="P236" t="n">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="Q236" t="inlineStr">
         <is>
@@ -34665,12 +34665,12 @@
       </c>
       <c r="AA236" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC236" t="inlineStr">
@@ -34763,7 +34763,7 @@
         </is>
       </c>
       <c r="P237" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q237" t="inlineStr">
         <is>
@@ -34817,12 +34817,12 @@
       </c>
       <c r="AA237" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC237" t="inlineStr">
@@ -34915,7 +34915,7 @@
         </is>
       </c>
       <c r="P238" t="n">
-        <v>-114</v>
+        <v>-115</v>
       </c>
       <c r="Q238" t="inlineStr">
         <is>
@@ -34969,12 +34969,12 @@
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB238" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC238" t="inlineStr">
@@ -35067,7 +35067,7 @@
         </is>
       </c>
       <c r="P239" t="n">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="Q239" t="inlineStr">
         <is>
@@ -35121,12 +35121,12 @@
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB239" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC239" t="inlineStr">
@@ -35211,7 +35211,7 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P240" t="inlineStr"/>
@@ -35228,7 +35228,7 @@
       </c>
       <c r="T240" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=18-CA-007512</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=18-CA-007512</t>
         </is>
       </c>
       <c r="U240" t="inlineStr">
@@ -35238,7 +35238,7 @@
       </c>
       <c r="V240" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W240" t="inlineStr">
@@ -35263,12 +35263,12 @@
       </c>
       <c r="AA240" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB240" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC240" t="inlineStr">
@@ -35349,7 +35349,7 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P241" t="n">
@@ -35362,7 +35362,7 @@
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S241" t="inlineStr">
@@ -35407,12 +35407,12 @@
       </c>
       <c r="AA241" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB241" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC241" t="inlineStr">
@@ -35497,7 +35497,7 @@
         </is>
       </c>
       <c r="P242" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q242" t="inlineStr">
         <is>
@@ -35551,12 +35551,12 @@
       </c>
       <c r="AA242" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC242" t="inlineStr">
@@ -35689,12 +35689,12 @@
       </c>
       <c r="AA243" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC243" t="inlineStr">
@@ -35779,7 +35779,7 @@
         </is>
       </c>
       <c r="P244" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q244" t="inlineStr">
         <is>
@@ -35833,12 +35833,12 @@
       </c>
       <c r="AA244" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC244" t="inlineStr">
@@ -35877,7 +35877,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>C. &amp; G. B█████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>K. &amp; G. G█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -35919,7 +35919,7 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P245" t="n">
@@ -35932,7 +35932,7 @@
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S245" t="inlineStr">
@@ -35977,17 +35977,17 @@
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC245" t="inlineStr">
         <is>
-          <t>C. &amp; G. B█████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>K. &amp; G. G█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD245" t="inlineStr">
@@ -36067,7 +36067,7 @@
         </is>
       </c>
       <c r="P246" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q246" t="inlineStr">
         <is>
@@ -36121,12 +36121,12 @@
       </c>
       <c r="AA246" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC246" t="inlineStr">
@@ -36211,7 +36211,7 @@
         </is>
       </c>
       <c r="P247" t="n">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="Q247" t="inlineStr">
         <is>
@@ -36265,12 +36265,12 @@
       </c>
       <c r="AA247" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC247" t="inlineStr">
@@ -36359,7 +36359,7 @@
         </is>
       </c>
       <c r="P248" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q248" t="inlineStr">
         <is>
@@ -36413,12 +36413,12 @@
       </c>
       <c r="AA248" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC248" t="inlineStr">
@@ -36507,7 +36507,7 @@
         </is>
       </c>
       <c r="P249" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q249" t="inlineStr">
         <is>
@@ -36561,12 +36561,12 @@
       </c>
       <c r="AA249" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC249" t="inlineStr">
@@ -36655,7 +36655,7 @@
         </is>
       </c>
       <c r="P250" t="n">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="Q250" t="inlineStr">
         <is>
@@ -36709,12 +36709,12 @@
       </c>
       <c r="AA250" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB250" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC250" t="inlineStr">
@@ -36757,7 +36757,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>G. &amp; S. S██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>H. &amp; S. S██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -36799,7 +36799,7 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P251" t="n">
@@ -36812,7 +36812,7 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S251" t="inlineStr">
@@ -36857,17 +36857,17 @@
       </c>
       <c r="AA251" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB251" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC251" t="inlineStr">
         <is>
-          <t>G. &amp; S. S██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>H. &amp; S. S██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD251" t="inlineStr">
@@ -36901,7 +36901,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>A. &amp; A. M███████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>R. &amp; S. M████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -36943,7 +36943,7 @@
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P252" t="n">
@@ -36956,7 +36956,7 @@
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S252" t="inlineStr">
@@ -37001,17 +37001,17 @@
       </c>
       <c r="AA252" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB252" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC252" t="inlineStr">
         <is>
-          <t>A. &amp; A. M███████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>R. &amp; S. M████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD252" t="inlineStr">
@@ -37091,7 +37091,7 @@
         </is>
       </c>
       <c r="P253" t="n">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="Q253" t="inlineStr">
         <is>
@@ -37145,12 +37145,12 @@
       </c>
       <c r="AA253" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB253" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC253" t="inlineStr">
@@ -37239,7 +37239,7 @@
         </is>
       </c>
       <c r="P254" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q254" t="inlineStr">
         <is>
@@ -37293,12 +37293,12 @@
       </c>
       <c r="AA254" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB254" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC254" t="inlineStr">
@@ -37341,7 +37341,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>L. &amp; S. R██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>R. &amp; R. R██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -37383,7 +37383,7 @@
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P255" t="n">
@@ -37396,7 +37396,7 @@
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S255" t="inlineStr">
@@ -37441,17 +37441,17 @@
       </c>
       <c r="AA255" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB255" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC255" t="inlineStr">
         <is>
-          <t>L. &amp; S. R██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>R. &amp; R. R██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD255" t="inlineStr">
@@ -37535,7 +37535,7 @@
         </is>
       </c>
       <c r="P256" t="n">
-        <v>-88</v>
+        <v>-89</v>
       </c>
       <c r="Q256" t="inlineStr">
         <is>
@@ -37589,12 +37589,12 @@
       </c>
       <c r="AA256" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB256" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC256" t="inlineStr">
@@ -37687,7 +37687,7 @@
         </is>
       </c>
       <c r="P257" t="n">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="Q257" t="inlineStr">
         <is>
@@ -37741,12 +37741,12 @@
       </c>
       <c r="AA257" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB257" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC257" t="inlineStr">
@@ -37839,7 +37839,7 @@
         </is>
       </c>
       <c r="P258" t="n">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="Q258" t="inlineStr">
         <is>
@@ -37893,12 +37893,12 @@
       </c>
       <c r="AA258" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB258" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC258" t="inlineStr">
@@ -37991,7 +37991,7 @@
         </is>
       </c>
       <c r="P259" t="n">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="Q259" t="inlineStr">
         <is>
@@ -38045,12 +38045,12 @@
       </c>
       <c r="AA259" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB259" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC259" t="inlineStr">
@@ -38143,7 +38143,7 @@
         </is>
       </c>
       <c r="P260" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q260" t="inlineStr">
         <is>
@@ -38197,12 +38197,12 @@
       </c>
       <c r="AA260" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB260" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC260" t="inlineStr">
@@ -38245,7 +38245,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>C. &amp; V. A███████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>C. &amp; V. C████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -38287,7 +38287,7 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P261" t="n">
@@ -38300,7 +38300,7 @@
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S261" t="inlineStr">
@@ -38345,17 +38345,17 @@
       </c>
       <c r="AA261" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB261" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC261" t="inlineStr">
         <is>
-          <t>C. &amp; V. A███████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>C. &amp; V. C████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD261" t="inlineStr">
@@ -38431,7 +38431,7 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P262" t="n">
@@ -38444,7 +38444,7 @@
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S262" t="inlineStr">
@@ -38489,12 +38489,12 @@
       </c>
       <c r="AA262" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB262" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC262" t="inlineStr">
@@ -38627,12 +38627,12 @@
       </c>
       <c r="AA263" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB263" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC263" t="inlineStr">
@@ -38725,7 +38725,7 @@
         </is>
       </c>
       <c r="P264" t="n">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="Q264" t="inlineStr">
         <is>
@@ -38779,12 +38779,12 @@
       </c>
       <c r="AA264" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB264" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC264" t="inlineStr">
@@ -38877,7 +38877,7 @@
         </is>
       </c>
       <c r="P265" t="n">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="Q265" t="inlineStr">
         <is>
@@ -38931,12 +38931,12 @@
       </c>
       <c r="AA265" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB265" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC265" t="inlineStr">
@@ -39025,7 +39025,7 @@
         </is>
       </c>
       <c r="P266" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q266" t="inlineStr">
         <is>
@@ -39079,12 +39079,12 @@
       </c>
       <c r="AA266" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB266" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC266" t="inlineStr">
@@ -39217,12 +39217,12 @@
       </c>
       <c r="AA267" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB267" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC267" t="inlineStr">
@@ -39311,7 +39311,7 @@
         </is>
       </c>
       <c r="P268" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q268" t="inlineStr">
         <is>
@@ -39365,12 +39365,12 @@
       </c>
       <c r="AA268" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB268" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC268" t="inlineStr">
@@ -39459,7 +39459,7 @@
         </is>
       </c>
       <c r="P269" t="n">
-        <v>-149</v>
+        <v>-150</v>
       </c>
       <c r="Q269" t="inlineStr">
         <is>
@@ -39513,12 +39513,12 @@
       </c>
       <c r="AA269" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB269" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC269" t="inlineStr">
@@ -39611,7 +39611,7 @@
         </is>
       </c>
       <c r="P270" t="n">
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="Q270" t="inlineStr">
         <is>
@@ -39665,12 +39665,12 @@
       </c>
       <c r="AA270" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB270" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC270" t="inlineStr">
@@ -39807,12 +39807,12 @@
       </c>
       <c r="AA271" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB271" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC271" t="inlineStr">
@@ -39897,7 +39897,7 @@
         </is>
       </c>
       <c r="P272" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q272" t="inlineStr">
         <is>
@@ -39951,12 +39951,12 @@
       </c>
       <c r="AA272" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC272" t="inlineStr">
@@ -40041,7 +40041,7 @@
         </is>
       </c>
       <c r="P273" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q273" t="inlineStr">
         <is>
@@ -40095,12 +40095,12 @@
       </c>
       <c r="AA273" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC273" t="inlineStr">
@@ -40189,7 +40189,7 @@
         </is>
       </c>
       <c r="P274" t="n">
-        <v>-88</v>
+        <v>-89</v>
       </c>
       <c r="Q274" t="inlineStr">
         <is>
@@ -40243,12 +40243,12 @@
       </c>
       <c r="AA274" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC274" t="inlineStr">
@@ -40333,7 +40333,7 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P275" t="inlineStr"/>
@@ -40350,7 +40350,7 @@
       </c>
       <c r="T275" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=09-CA-009881</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=09-CA-009881</t>
         </is>
       </c>
       <c r="U275" t="inlineStr">
@@ -40360,7 +40360,7 @@
       </c>
       <c r="V275" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W275" t="inlineStr">
@@ -40385,12 +40385,12 @@
       </c>
       <c r="AA275" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC275" t="inlineStr">
@@ -40479,7 +40479,7 @@
         </is>
       </c>
       <c r="P276" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q276" t="inlineStr">
         <is>
@@ -40533,12 +40533,12 @@
       </c>
       <c r="AA276" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC276" t="inlineStr">
@@ -40631,7 +40631,7 @@
         </is>
       </c>
       <c r="P277" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q277" t="inlineStr">
         <is>
@@ -40685,12 +40685,12 @@
       </c>
       <c r="AA277" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB277" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC277" t="inlineStr">
@@ -40775,7 +40775,7 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P278" t="n">
@@ -40788,7 +40788,7 @@
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S278" t="inlineStr">
@@ -40833,12 +40833,12 @@
       </c>
       <c r="AA278" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB278" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC278" t="inlineStr">
@@ -40919,7 +40919,7 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P279" t="n">
@@ -40932,7 +40932,7 @@
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S279" t="inlineStr">
@@ -40977,12 +40977,12 @@
       </c>
       <c r="AA279" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB279" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC279" t="inlineStr">
@@ -41071,7 +41071,7 @@
         </is>
       </c>
       <c r="P280" t="n">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="Q280" t="inlineStr">
         <is>
@@ -41125,12 +41125,12 @@
       </c>
       <c r="AA280" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB280" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC280" t="inlineStr">
@@ -41173,7 +41173,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>D. &amp; W. B██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>E. &amp; B. B██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -41215,7 +41215,7 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P281" t="n">
@@ -41228,7 +41228,7 @@
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S281" t="inlineStr">
@@ -41273,17 +41273,17 @@
       </c>
       <c r="AA281" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB281" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC281" t="inlineStr">
         <is>
-          <t>D. &amp; W. B██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>E. &amp; B. B██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD281" t="inlineStr">
@@ -41367,7 +41367,7 @@
         </is>
       </c>
       <c r="P282" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q282" t="inlineStr">
         <is>
@@ -41421,12 +41421,12 @@
       </c>
       <c r="AA282" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB282" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC282" t="inlineStr">
@@ -41519,7 +41519,7 @@
         </is>
       </c>
       <c r="P283" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q283" t="inlineStr">
         <is>
@@ -41573,12 +41573,12 @@
       </c>
       <c r="AA283" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB283" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC283" t="inlineStr">
@@ -41671,7 +41671,7 @@
         </is>
       </c>
       <c r="P284" t="n">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="Q284" t="inlineStr">
         <is>
@@ -41725,12 +41725,12 @@
       </c>
       <c r="AA284" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB284" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC284" t="inlineStr">
@@ -41815,7 +41815,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P285" t="n">
@@ -41828,7 +41828,7 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S285" t="inlineStr">
@@ -41873,12 +41873,12 @@
       </c>
       <c r="AA285" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB285" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC285" t="inlineStr">
@@ -41959,7 +41959,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P286" t="inlineStr"/>
@@ -41976,7 +41976,7 @@
       </c>
       <c r="T286" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=24-CA-000685</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=24-CA-000685</t>
         </is>
       </c>
       <c r="U286" t="inlineStr">
@@ -41986,7 +41986,7 @@
       </c>
       <c r="V286" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W286" t="inlineStr">
@@ -42011,12 +42011,12 @@
       </c>
       <c r="AA286" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB286" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC286" t="inlineStr">
@@ -42105,7 +42105,7 @@
         </is>
       </c>
       <c r="P287" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q287" t="inlineStr">
         <is>
@@ -42159,12 +42159,12 @@
       </c>
       <c r="AA287" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB287" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC287" t="inlineStr">
@@ -42257,7 +42257,7 @@
         </is>
       </c>
       <c r="P288" t="n">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="Q288" t="inlineStr">
         <is>
@@ -42311,12 +42311,12 @@
       </c>
       <c r="AA288" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB288" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC288" t="inlineStr">
@@ -42401,7 +42401,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P289" t="n">
@@ -42414,7 +42414,7 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S289" t="inlineStr">
@@ -42459,12 +42459,12 @@
       </c>
       <c r="AA289" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB289" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC289" t="inlineStr">
@@ -42553,7 +42553,7 @@
         </is>
       </c>
       <c r="P290" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q290" t="inlineStr">
         <is>
@@ -42607,12 +42607,12 @@
       </c>
       <c r="AA290" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB290" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC290" t="inlineStr">
@@ -42697,7 +42697,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P291" t="n">
@@ -42710,7 +42710,7 @@
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S291" t="inlineStr">
@@ -42755,12 +42755,12 @@
       </c>
       <c r="AA291" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB291" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC291" t="inlineStr">
@@ -42849,7 +42849,7 @@
         </is>
       </c>
       <c r="P292" t="n">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="Q292" t="inlineStr">
         <is>
@@ -42903,12 +42903,12 @@
       </c>
       <c r="AA292" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB292" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC292" t="inlineStr">
@@ -43001,7 +43001,7 @@
         </is>
       </c>
       <c r="P293" t="n">
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="Q293" t="inlineStr">
         <is>
@@ -43055,12 +43055,12 @@
       </c>
       <c r="AA293" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB293" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC293" t="inlineStr">
@@ -43197,12 +43197,12 @@
       </c>
       <c r="AA294" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB294" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC294" t="inlineStr">
@@ -43291,7 +43291,7 @@
         </is>
       </c>
       <c r="P295" t="n">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="Q295" t="inlineStr">
         <is>
@@ -43345,12 +43345,12 @@
       </c>
       <c r="AA295" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB295" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC295" t="inlineStr">
@@ -43435,7 +43435,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P296" t="n">
@@ -43448,7 +43448,7 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S296" t="inlineStr">
@@ -43493,12 +43493,12 @@
       </c>
       <c r="AA296" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB296" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC296" t="inlineStr">
@@ -43587,7 +43587,7 @@
         </is>
       </c>
       <c r="P297" t="n">
-        <v>-88</v>
+        <v>-89</v>
       </c>
       <c r="Q297" t="inlineStr">
         <is>
@@ -43641,12 +43641,12 @@
       </c>
       <c r="AA297" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB297" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC297" t="inlineStr">
@@ -43731,7 +43731,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P298" t="inlineStr"/>
@@ -43748,7 +43748,7 @@
       </c>
       <c r="T298" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=24-CA-005012</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=24-CA-005012</t>
         </is>
       </c>
       <c r="U298" t="inlineStr">
@@ -43758,7 +43758,7 @@
       </c>
       <c r="V298" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W298" t="inlineStr">
@@ -43783,12 +43783,12 @@
       </c>
       <c r="AA298" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB298" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC298" t="inlineStr">
@@ -43877,7 +43877,7 @@
         </is>
       </c>
       <c r="P299" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q299" t="inlineStr">
         <is>
@@ -43931,12 +43931,12 @@
       </c>
       <c r="AA299" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC299" t="inlineStr">
@@ -44025,7 +44025,7 @@
         </is>
       </c>
       <c r="P300" t="n">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q300" t="inlineStr">
         <is>
@@ -44079,12 +44079,12 @@
       </c>
       <c r="AA300" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB300" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC300" t="inlineStr">
@@ -44217,12 +44217,12 @@
       </c>
       <c r="AA301" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB301" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC301" t="inlineStr">
@@ -44315,7 +44315,7 @@
         </is>
       </c>
       <c r="P302" t="n">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="Q302" t="inlineStr">
         <is>
@@ -44369,12 +44369,12 @@
       </c>
       <c r="AA302" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB302" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC302" t="inlineStr">
@@ -44463,7 +44463,7 @@
         </is>
       </c>
       <c r="P303" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q303" t="inlineStr">
         <is>
@@ -44517,12 +44517,12 @@
       </c>
       <c r="AA303" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB303" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC303" t="inlineStr">
@@ -44611,7 +44611,7 @@
         </is>
       </c>
       <c r="P304" t="n">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="Q304" t="inlineStr">
         <is>
@@ -44665,12 +44665,12 @@
       </c>
       <c r="AA304" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB304" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC304" t="inlineStr">
@@ -44807,12 +44807,12 @@
       </c>
       <c r="AA305" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB305" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC305" t="inlineStr">
@@ -44901,7 +44901,7 @@
         </is>
       </c>
       <c r="P306" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q306" t="inlineStr">
         <is>
@@ -44955,12 +44955,12 @@
       </c>
       <c r="AA306" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB306" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC306" t="inlineStr">
@@ -45053,7 +45053,7 @@
         </is>
       </c>
       <c r="P307" t="n">
-        <v>-88</v>
+        <v>-89</v>
       </c>
       <c r="Q307" t="inlineStr">
         <is>
@@ -45107,12 +45107,12 @@
       </c>
       <c r="AA307" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB307" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC307" t="inlineStr">
@@ -45197,7 +45197,7 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P308" t="n">
@@ -45210,7 +45210,7 @@
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S308" t="inlineStr">
@@ -45255,12 +45255,12 @@
       </c>
       <c r="AA308" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC308" t="inlineStr">
@@ -45345,7 +45345,7 @@
         </is>
       </c>
       <c r="P309" t="n">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="Q309" t="inlineStr">
         <is>
@@ -45399,12 +45399,12 @@
       </c>
       <c r="AA309" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB309" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC309" t="inlineStr">
@@ -45489,7 +45489,7 @@
         </is>
       </c>
       <c r="P310" t="n">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q310" t="inlineStr">
         <is>
@@ -45543,12 +45543,12 @@
       </c>
       <c r="AA310" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB310" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC310" t="inlineStr">
@@ -45633,7 +45633,7 @@
         </is>
       </c>
       <c r="P311" t="n">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Q311" t="inlineStr">
         <is>
@@ -45687,12 +45687,12 @@
       </c>
       <c r="AA311" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC311" t="inlineStr">
@@ -45773,7 +45773,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P312" t="n">
@@ -45786,7 +45786,7 @@
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S312" t="inlineStr">
@@ -45831,12 +45831,12 @@
       </c>
       <c r="AA312" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC312" t="inlineStr">
@@ -45925,7 +45925,7 @@
         </is>
       </c>
       <c r="P313" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q313" t="inlineStr">
         <is>
@@ -45979,12 +45979,12 @@
       </c>
       <c r="AA313" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB313" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC313" t="inlineStr">
@@ -46073,7 +46073,7 @@
         </is>
       </c>
       <c r="P314" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q314" t="inlineStr">
         <is>
@@ -46127,12 +46127,12 @@
       </c>
       <c r="AA314" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB314" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC314" t="inlineStr">
@@ -46221,7 +46221,7 @@
         </is>
       </c>
       <c r="P315" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q315" t="inlineStr">
         <is>
@@ -46275,12 +46275,12 @@
       </c>
       <c r="AA315" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB315" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC315" t="inlineStr">
@@ -46373,7 +46373,7 @@
         </is>
       </c>
       <c r="P316" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q316" t="inlineStr">
         <is>
@@ -46427,12 +46427,12 @@
       </c>
       <c r="AA316" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB316" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC316" t="inlineStr">
@@ -46517,7 +46517,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P317" t="n">
@@ -46530,7 +46530,7 @@
       </c>
       <c r="R317" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S317" t="inlineStr">
@@ -46575,12 +46575,12 @@
       </c>
       <c r="AA317" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB317" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC317" t="inlineStr">
@@ -46669,7 +46669,7 @@
         </is>
       </c>
       <c r="P318" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q318" t="inlineStr">
         <is>
@@ -46723,12 +46723,12 @@
       </c>
       <c r="AA318" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB318" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC318" t="inlineStr">
@@ -46821,7 +46821,7 @@
         </is>
       </c>
       <c r="P319" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q319" t="inlineStr">
         <is>
@@ -46875,12 +46875,12 @@
       </c>
       <c r="AA319" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB319" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC319" t="inlineStr">
@@ -46969,7 +46969,7 @@
         </is>
       </c>
       <c r="P320" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q320" t="inlineStr">
         <is>
@@ -47023,12 +47023,12 @@
       </c>
       <c r="AA320" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB320" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC320" t="inlineStr">
@@ -47117,7 +47117,7 @@
         </is>
       </c>
       <c r="P321" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q321" t="inlineStr">
         <is>
@@ -47171,12 +47171,12 @@
       </c>
       <c r="AA321" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB321" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC321" t="inlineStr">
@@ -47269,7 +47269,7 @@
         </is>
       </c>
       <c r="P322" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q322" t="inlineStr">
         <is>
@@ -47323,12 +47323,12 @@
       </c>
       <c r="AA322" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB322" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC322" t="inlineStr">
@@ -47421,7 +47421,7 @@
         </is>
       </c>
       <c r="P323" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q323" t="inlineStr">
         <is>
@@ -47475,12 +47475,12 @@
       </c>
       <c r="AA323" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB323" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC323" t="inlineStr">
@@ -47573,7 +47573,7 @@
         </is>
       </c>
       <c r="P324" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q324" t="inlineStr">
         <is>
@@ -47627,12 +47627,12 @@
       </c>
       <c r="AA324" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB324" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC324" t="inlineStr">
@@ -47717,7 +47717,7 @@
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P325" t="n">
@@ -47730,7 +47730,7 @@
       </c>
       <c r="R325" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S325" t="inlineStr">
@@ -47775,12 +47775,12 @@
       </c>
       <c r="AA325" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB325" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC325" t="inlineStr">
@@ -47869,7 +47869,7 @@
         </is>
       </c>
       <c r="P326" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q326" t="inlineStr">
         <is>
@@ -47923,12 +47923,12 @@
       </c>
       <c r="AA326" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB326" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC326" t="inlineStr">
@@ -48021,7 +48021,7 @@
         </is>
       </c>
       <c r="P327" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q327" t="inlineStr">
         <is>
@@ -48075,12 +48075,12 @@
       </c>
       <c r="AA327" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB327" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC327" t="inlineStr">
@@ -48165,7 +48165,7 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P328" t="n">
@@ -48178,7 +48178,7 @@
       </c>
       <c r="R328" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S328" t="inlineStr">
@@ -48223,12 +48223,12 @@
       </c>
       <c r="AA328" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB328" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC328" t="inlineStr">
@@ -48313,7 +48313,7 @@
         </is>
       </c>
       <c r="P329" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q329" t="inlineStr">
         <is>
@@ -48367,12 +48367,12 @@
       </c>
       <c r="AA329" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB329" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC329" t="inlineStr">
@@ -48457,7 +48457,7 @@
         </is>
       </c>
       <c r="P330" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q330" t="inlineStr">
         <is>
@@ -48511,12 +48511,12 @@
       </c>
       <c r="AA330" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB330" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC330" t="inlineStr">
@@ -48555,7 +48555,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>V. &amp; W. L████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>M. &amp; A. G████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
@@ -48597,7 +48597,7 @@
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P331" t="n">
@@ -48610,7 +48610,7 @@
       </c>
       <c r="R331" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S331" t="inlineStr">
@@ -48655,17 +48655,17 @@
       </c>
       <c r="AA331" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB331" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC331" t="inlineStr">
         <is>
-          <t>V. &amp; W. L████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>M. &amp; A. G████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD331" t="inlineStr">
@@ -48745,7 +48745,7 @@
         </is>
       </c>
       <c r="P332" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q332" t="inlineStr">
         <is>
@@ -48799,12 +48799,12 @@
       </c>
       <c r="AA332" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB332" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC332" t="inlineStr">
@@ -48889,7 +48889,7 @@
         </is>
       </c>
       <c r="P333" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q333" t="inlineStr">
         <is>
@@ -48943,12 +48943,12 @@
       </c>
       <c r="AA333" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB333" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC333" t="inlineStr">
@@ -49037,7 +49037,7 @@
         </is>
       </c>
       <c r="P334" t="n">
-        <v>-88</v>
+        <v>-89</v>
       </c>
       <c r="Q334" t="inlineStr">
         <is>
@@ -49091,12 +49091,12 @@
       </c>
       <c r="AA334" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB334" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC334" t="inlineStr">
@@ -49189,7 +49189,7 @@
         </is>
       </c>
       <c r="P335" t="n">
-        <v>-88</v>
+        <v>-89</v>
       </c>
       <c r="Q335" t="inlineStr">
         <is>
@@ -49243,12 +49243,12 @@
       </c>
       <c r="AA335" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB335" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC335" t="inlineStr">
@@ -49333,7 +49333,7 @@
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P336" t="inlineStr"/>
@@ -49350,7 +49350,7 @@
       </c>
       <c r="T336" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=23-CA-000671</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=23-CA-000671</t>
         </is>
       </c>
       <c r="U336" t="inlineStr">
@@ -49360,7 +49360,7 @@
       </c>
       <c r="V336" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W336" t="inlineStr">
@@ -49385,12 +49385,12 @@
       </c>
       <c r="AA336" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB336" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC336" t="inlineStr">
@@ -49479,7 +49479,7 @@
         </is>
       </c>
       <c r="P337" t="n">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="Q337" t="inlineStr">
         <is>
@@ -49533,12 +49533,12 @@
       </c>
       <c r="AA337" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB337" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC337" t="inlineStr">
@@ -49631,7 +49631,7 @@
         </is>
       </c>
       <c r="P338" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q338" t="inlineStr">
         <is>
@@ -49685,12 +49685,12 @@
       </c>
       <c r="AA338" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB338" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC338" t="inlineStr">
@@ -49775,7 +49775,7 @@
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P339" t="n">
@@ -49788,7 +49788,7 @@
       </c>
       <c r="R339" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S339" t="inlineStr">
@@ -49833,12 +49833,12 @@
       </c>
       <c r="AA339" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB339" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC339" t="inlineStr">
@@ -49927,7 +49927,7 @@
         </is>
       </c>
       <c r="P340" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q340" t="inlineStr">
         <is>
@@ -49981,12 +49981,12 @@
       </c>
       <c r="AA340" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB340" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC340" t="inlineStr">
@@ -50079,7 +50079,7 @@
         </is>
       </c>
       <c r="P341" t="n">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="Q341" t="inlineStr">
         <is>
@@ -50133,12 +50133,12 @@
       </c>
       <c r="AA341" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB341" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC341" t="inlineStr">
@@ -50227,7 +50227,7 @@
         </is>
       </c>
       <c r="P342" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q342" t="inlineStr">
         <is>
@@ -50281,12 +50281,12 @@
       </c>
       <c r="AA342" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB342" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC342" t="inlineStr">
@@ -50375,7 +50375,7 @@
         </is>
       </c>
       <c r="P343" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q343" t="inlineStr">
         <is>
@@ -50429,12 +50429,12 @@
       </c>
       <c r="AA343" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB343" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC343" t="inlineStr">
@@ -50527,7 +50527,7 @@
         </is>
       </c>
       <c r="P344" t="n">
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="Q344" t="inlineStr">
         <is>
@@ -50581,12 +50581,12 @@
       </c>
       <c r="AA344" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB344" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC344" t="inlineStr">
@@ -50679,7 +50679,7 @@
         </is>
       </c>
       <c r="P345" t="n">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="Q345" t="inlineStr">
         <is>
@@ -50733,12 +50733,12 @@
       </c>
       <c r="AA345" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB345" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC345" t="inlineStr">
@@ -50831,7 +50831,7 @@
         </is>
       </c>
       <c r="P346" t="n">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="Q346" t="inlineStr">
         <is>
@@ -50885,12 +50885,12 @@
       </c>
       <c r="AA346" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB346" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC346" t="inlineStr">
@@ -50983,7 +50983,7 @@
         </is>
       </c>
       <c r="P347" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q347" t="inlineStr">
         <is>
@@ -51037,12 +51037,12 @@
       </c>
       <c r="AA347" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB347" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC347" t="inlineStr">
@@ -51135,7 +51135,7 @@
         </is>
       </c>
       <c r="P348" t="n">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="Q348" t="inlineStr">
         <is>
@@ -51189,12 +51189,12 @@
       </c>
       <c r="AA348" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB348" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC348" t="inlineStr">
@@ -51287,7 +51287,7 @@
         </is>
       </c>
       <c r="P349" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q349" t="inlineStr">
         <is>
@@ -51341,12 +51341,12 @@
       </c>
       <c r="AA349" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB349" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC349" t="inlineStr">
@@ -51439,7 +51439,7 @@
         </is>
       </c>
       <c r="P350" t="n">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="Q350" t="inlineStr">
         <is>
@@ -51493,12 +51493,12 @@
       </c>
       <c r="AA350" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB350" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC350" t="inlineStr">
@@ -51591,7 +51591,7 @@
         </is>
       </c>
       <c r="P351" t="n">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="Q351" t="inlineStr">
         <is>
@@ -51645,12 +51645,12 @@
       </c>
       <c r="AA351" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB351" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC351" t="inlineStr">
@@ -51743,7 +51743,7 @@
         </is>
       </c>
       <c r="P352" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q352" t="inlineStr">
         <is>
@@ -51797,12 +51797,12 @@
       </c>
       <c r="AA352" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB352" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC352" t="inlineStr">
@@ -51895,7 +51895,7 @@
         </is>
       </c>
       <c r="P353" t="n">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="Q353" t="inlineStr">
         <is>
@@ -51949,12 +51949,12 @@
       </c>
       <c r="AA353" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB353" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC353" t="inlineStr">
@@ -52047,7 +52047,7 @@
         </is>
       </c>
       <c r="P354" t="n">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Q354" t="inlineStr">
         <is>
@@ -52101,12 +52101,12 @@
       </c>
       <c r="AA354" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB354" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC354" t="inlineStr">
@@ -52191,7 +52191,7 @@
       </c>
       <c r="O355" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P355" t="inlineStr"/>
@@ -52208,7 +52208,7 @@
       </c>
       <c r="T355" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=22-CA-007538</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=22-CA-007538</t>
         </is>
       </c>
       <c r="U355" t="inlineStr">
@@ -52218,7 +52218,7 @@
       </c>
       <c r="V355" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W355" t="inlineStr">
@@ -52243,12 +52243,12 @@
       </c>
       <c r="AA355" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB355" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC355" t="inlineStr">
@@ -52333,7 +52333,7 @@
         </is>
       </c>
       <c r="P356" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q356" t="inlineStr">
         <is>
@@ -52387,12 +52387,12 @@
       </c>
       <c r="AA356" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB356" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC356" t="inlineStr">
@@ -52481,7 +52481,7 @@
         </is>
       </c>
       <c r="P357" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q357" t="inlineStr">
         <is>
@@ -52535,12 +52535,12 @@
       </c>
       <c r="AA357" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB357" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC357" t="inlineStr">
@@ -52633,7 +52633,7 @@
         </is>
       </c>
       <c r="P358" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q358" t="inlineStr">
         <is>
@@ -52687,12 +52687,12 @@
       </c>
       <c r="AA358" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB358" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC358" t="inlineStr">
@@ -52781,7 +52781,7 @@
         </is>
       </c>
       <c r="P359" t="n">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q359" t="inlineStr">
         <is>
@@ -52835,12 +52835,12 @@
       </c>
       <c r="AA359" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB359" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC359" t="inlineStr">
@@ -52921,7 +52921,7 @@
       </c>
       <c r="O360" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P360" t="n">
@@ -52934,7 +52934,7 @@
       </c>
       <c r="R360" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S360" t="inlineStr">
@@ -52979,12 +52979,12 @@
       </c>
       <c r="AA360" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB360" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC360" t="inlineStr">
@@ -53073,7 +53073,7 @@
         </is>
       </c>
       <c r="P361" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q361" t="inlineStr">
         <is>
@@ -53127,12 +53127,12 @@
       </c>
       <c r="AA361" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB361" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC361" t="inlineStr">
@@ -53269,12 +53269,12 @@
       </c>
       <c r="AA362" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB362" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC362" t="inlineStr">
@@ -53359,7 +53359,7 @@
         </is>
       </c>
       <c r="P363" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q363" t="inlineStr">
         <is>
@@ -53413,12 +53413,12 @@
       </c>
       <c r="AA363" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB363" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC363" t="inlineStr">
@@ -53503,7 +53503,7 @@
         </is>
       </c>
       <c r="P364" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q364" t="inlineStr">
         <is>
@@ -53557,12 +53557,12 @@
       </c>
       <c r="AA364" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB364" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC364" t="inlineStr">
@@ -53647,7 +53647,7 @@
         </is>
       </c>
       <c r="P365" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q365" t="inlineStr">
         <is>
@@ -53701,12 +53701,12 @@
       </c>
       <c r="AA365" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB365" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC365" t="inlineStr">
@@ -53791,7 +53791,7 @@
         </is>
       </c>
       <c r="P366" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q366" t="inlineStr">
         <is>
@@ -53845,12 +53845,12 @@
       </c>
       <c r="AA366" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB366" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC366" t="inlineStr">
@@ -53935,7 +53935,7 @@
         </is>
       </c>
       <c r="P367" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q367" t="inlineStr">
         <is>
@@ -53989,12 +53989,12 @@
       </c>
       <c r="AA367" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB367" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC367" t="inlineStr">
@@ -54079,7 +54079,7 @@
         </is>
       </c>
       <c r="P368" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q368" t="inlineStr">
         <is>
@@ -54133,12 +54133,12 @@
       </c>
       <c r="AA368" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB368" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC368" t="inlineStr">
@@ -54219,7 +54219,7 @@
       </c>
       <c r="O369" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P369" t="inlineStr"/>
@@ -54236,7 +54236,7 @@
       </c>
       <c r="T369" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=25-CA-005347</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=25-CA-005347</t>
         </is>
       </c>
       <c r="U369" t="inlineStr">
@@ -54246,7 +54246,7 @@
       </c>
       <c r="V369" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W369" t="inlineStr">
@@ -54271,12 +54271,12 @@
       </c>
       <c r="AA369" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB369" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC369" t="inlineStr">

--- a/site/exports/Tri_State_Core_Surplus_Feed.xlsx
+++ b/site/exports/Tri_State_Core_Surplus_Feed.xlsx
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -855,12 +855,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>P. &amp; B. A██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>P. &amp; B. K████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -999,17 +999,17 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>P. &amp; B. A██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>P. &amp; B. K████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1575,12 +1575,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1727,12 +1727,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1869,12 +1869,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=23-CA-016325</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=23-CA-016325</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -2007,12 +2007,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -2155,12 +2155,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-89</v>
+        <v>-90</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2307,12 +2307,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2603,12 +2603,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2755,12 +2755,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2907,12 +2907,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -3203,12 +3203,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3493,12 +3493,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3635,12 +3635,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>J. &amp; W. S███████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>J. &amp; C. S██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3779,17 +3779,17 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>J. &amp; W. S███████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>J. &amp; C. S██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>C. &amp; F. S████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>R. &amp; R. C████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P25" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -4067,17 +4067,17 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>C. &amp; F. S████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>R. &amp; R. C████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4305,7 +4305,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>-89</v>
+        <v>-90</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4359,12 +4359,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>S. &amp; F. C█████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>I. &amp; R. A███████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P28" t="n">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -4507,17 +4507,17 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>S. &amp; F. C█████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>I. &amp; R. A███████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4655,12 +4655,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4807,12 +4807,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4905,7 +4905,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4959,12 +4959,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -5111,12 +5111,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -5209,7 +5209,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -5263,12 +5263,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P34" t="inlineStr"/>
@@ -5370,7 +5370,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=26-CA-006185</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=26-CA-006185</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -5405,12 +5405,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-52</v>
+        <v>-53</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5647,7 +5647,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5701,12 +5701,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -5929,7 +5929,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -6077,7 +6077,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -6131,12 +6131,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -6229,7 +6229,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -6283,12 +6283,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -6435,12 +6435,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -6533,7 +6533,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -6587,12 +6587,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -6739,12 +6739,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -6881,12 +6881,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -7029,12 +7029,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -7127,7 +7127,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -7181,12 +7181,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -7329,12 +7329,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -7423,7 +7423,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -7477,12 +7477,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -7713,7 +7713,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -7767,12 +7767,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -7865,7 +7865,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -7919,12 +7919,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -8067,12 +8067,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P53" t="inlineStr"/>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=24-CA-001841</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=24-CA-001841</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -8349,12 +8349,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -8443,7 +8443,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -8639,12 +8639,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -8733,7 +8733,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>-52</v>
+        <v>-53</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -8787,12 +8787,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -8881,7 +8881,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -8935,12 +8935,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -9021,7 +9021,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -9169,7 +9169,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -9223,12 +9223,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -9317,7 +9317,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -9371,12 +9371,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -9513,12 +9513,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -9603,7 +9603,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -9657,12 +9657,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -9894,7 +9894,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -9939,12 +9939,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -10029,7 +10029,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -10083,12 +10083,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -10173,7 +10173,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -10227,12 +10227,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P68" t="n">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -10509,12 +10509,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -10599,7 +10599,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -10653,12 +10653,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
@@ -10791,12 +10791,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -10929,12 +10929,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
@@ -10973,7 +10973,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Y. &amp; M. C█████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>B. &amp; K. C█████████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -11015,7 +11015,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P73" t="n">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -11073,17 +11073,17 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Y. &amp; M. C█████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>B. &amp; K. C█████████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD73" t="inlineStr">
@@ -11167,7 +11167,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -11221,12 +11221,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
@@ -11315,7 +11315,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -11369,12 +11369,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
@@ -11455,7 +11455,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P76" t="n">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -11657,12 +11657,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
@@ -11747,7 +11747,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -11801,12 +11801,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
@@ -11887,7 +11887,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P79" t="n">
@@ -11900,7 +11900,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -11945,12 +11945,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
@@ -12173,7 +12173,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -12227,12 +12227,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
@@ -12365,12 +12365,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
@@ -12459,7 +12459,7 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -12513,12 +12513,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -12611,7 +12611,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>-52</v>
+        <v>-53</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
@@ -12763,7 +12763,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -12817,12 +12817,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
@@ -12959,12 +12959,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
@@ -13097,12 +13097,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
@@ -13187,7 +13187,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -13241,12 +13241,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
@@ -13331,7 +13331,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -13385,12 +13385,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -13475,7 +13475,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -13529,12 +13529,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -13615,7 +13615,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P91" t="n">
@@ -13628,7 +13628,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -13673,12 +13673,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
@@ -13759,7 +13759,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P92" t="n">
@@ -13772,7 +13772,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
@@ -13907,7 +13907,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -13961,12 +13961,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
@@ -14051,7 +14051,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -14105,12 +14105,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
@@ -14195,7 +14195,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -14249,12 +14249,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
@@ -14343,7 +14343,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -14397,12 +14397,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
@@ -14487,7 +14487,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P97" t="inlineStr"/>
@@ -14504,7 +14504,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=23-CA-017541</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=23-CA-017541</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -14514,7 +14514,7 @@
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
@@ -14539,12 +14539,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
@@ -14625,7 +14625,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P98" t="n">
@@ -14638,7 +14638,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
@@ -14773,7 +14773,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -14827,12 +14827,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
@@ -14921,7 +14921,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -14975,12 +14975,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
@@ -15069,7 +15069,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -15123,12 +15123,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
@@ -15213,7 +15213,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -15267,12 +15267,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
@@ -15357,7 +15357,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -15411,12 +15411,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
@@ -15497,7 +15497,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P104" t="inlineStr"/>
@@ -15514,7 +15514,7 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=21-CA-005559</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=21-CA-005559</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
@@ -15524,7 +15524,7 @@
       </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W104" t="inlineStr">
@@ -15549,12 +15549,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
@@ -15643,7 +15643,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -15697,12 +15697,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
@@ -15791,7 +15791,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -15845,12 +15845,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
@@ -15935,7 +15935,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -15989,12 +15989,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
@@ -16075,7 +16075,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -16088,7 +16088,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
@@ -16133,12 +16133,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
@@ -16219,7 +16219,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -16232,7 +16232,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
@@ -16277,12 +16277,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
@@ -16367,7 +16367,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -16421,12 +16421,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
@@ -16511,7 +16511,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -16565,12 +16565,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
@@ -16659,7 +16659,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -16713,12 +16713,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
@@ -16811,7 +16811,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -16865,12 +16865,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
@@ -16959,7 +16959,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -17013,12 +17013,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
@@ -17099,7 +17099,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -17112,7 +17112,7 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
@@ -17157,12 +17157,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
@@ -17251,7 +17251,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -17305,12 +17305,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
@@ -17447,12 +17447,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
@@ -17541,7 +17541,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -17595,12 +17595,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
@@ -17685,7 +17685,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -17739,12 +17739,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
@@ -17877,12 +17877,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
@@ -17967,7 +17967,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -18021,12 +18021,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
@@ -18159,12 +18159,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
@@ -18297,12 +18297,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
@@ -18387,7 +18387,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -18441,12 +18441,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
@@ -18535,7 +18535,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -18589,12 +18589,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
@@ -18679,7 +18679,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P126" t="n">
@@ -18692,7 +18692,7 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
@@ -18737,12 +18737,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr">
@@ -18875,12 +18875,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr">
@@ -18965,7 +18965,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P128" t="n">
@@ -18978,7 +18978,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
@@ -19023,12 +19023,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr">
@@ -19113,7 +19113,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -19167,12 +19167,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr">
@@ -19257,7 +19257,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -19311,12 +19311,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr">
@@ -19405,7 +19405,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -19459,12 +19459,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr">
@@ -19549,7 +19549,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P132" t="n">
@@ -19562,7 +19562,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
@@ -19607,12 +19607,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr">
@@ -19697,7 +19697,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -19751,12 +19751,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
@@ -19889,12 +19889,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
@@ -19979,7 +19979,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -20033,12 +20033,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC135" t="inlineStr">
@@ -20119,7 +20119,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P136" t="n">
@@ -20132,7 +20132,7 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S136" t="inlineStr">
@@ -20177,12 +20177,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr">
@@ -20315,12 +20315,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr">
@@ -20405,7 +20405,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -20459,12 +20459,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr">
@@ -20545,7 +20545,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P139" t="inlineStr"/>
@@ -20562,7 +20562,7 @@
       </c>
       <c r="T139" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=21-CA-004936</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=21-CA-004936</t>
         </is>
       </c>
       <c r="U139" t="inlineStr">
@@ -20572,7 +20572,7 @@
       </c>
       <c r="V139" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W139" t="inlineStr">
@@ -20597,12 +20597,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr">
@@ -20735,12 +20735,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
@@ -20825,7 +20825,7 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
@@ -20879,12 +20879,12 @@
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC141" t="inlineStr">
@@ -20973,7 +20973,7 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
@@ -21027,12 +21027,12 @@
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC142" t="inlineStr">
@@ -21125,7 +21125,7 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
@@ -21179,12 +21179,12 @@
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC143" t="inlineStr">
@@ -21277,7 +21277,7 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
@@ -21331,12 +21331,12 @@
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC144" t="inlineStr">
@@ -21425,7 +21425,7 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
@@ -21479,12 +21479,12 @@
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC145" t="inlineStr">
@@ -21565,7 +21565,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P146" t="n">
@@ -21578,7 +21578,7 @@
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S146" t="inlineStr">
@@ -21623,12 +21623,12 @@
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC146" t="inlineStr">
@@ -21717,7 +21717,7 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
@@ -21771,12 +21771,12 @@
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC147" t="inlineStr">
@@ -21865,7 +21865,7 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
@@ -21919,12 +21919,12 @@
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC148" t="inlineStr">
@@ -22005,7 +22005,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P149" t="n">
@@ -22018,7 +22018,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S149" t="inlineStr">
@@ -22063,12 +22063,12 @@
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC149" t="inlineStr">
@@ -22153,7 +22153,7 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
@@ -22207,12 +22207,12 @@
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC150" t="inlineStr">
@@ -22301,7 +22301,7 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
@@ -22355,12 +22355,12 @@
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC151" t="inlineStr">
@@ -22445,7 +22445,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P152" t="n">
@@ -22458,7 +22458,7 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S152" t="inlineStr">
@@ -22503,12 +22503,12 @@
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC152" t="inlineStr">
@@ -22593,7 +22593,7 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
@@ -22647,12 +22647,12 @@
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC153" t="inlineStr">
@@ -22737,7 +22737,7 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
@@ -22791,12 +22791,12 @@
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC154" t="inlineStr">
@@ -22881,7 +22881,7 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
@@ -22935,12 +22935,12 @@
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC155" t="inlineStr">
@@ -23029,7 +23029,7 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
@@ -23083,12 +23083,12 @@
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC156" t="inlineStr">
@@ -23173,7 +23173,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P157" t="inlineStr"/>
@@ -23190,7 +23190,7 @@
       </c>
       <c r="T157" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=23-CA-014882</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=23-CA-014882</t>
         </is>
       </c>
       <c r="U157" t="inlineStr">
@@ -23200,7 +23200,7 @@
       </c>
       <c r="V157" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
@@ -23225,12 +23225,12 @@
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC157" t="inlineStr">
@@ -23315,7 +23315,7 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
@@ -23369,12 +23369,12 @@
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC158" t="inlineStr">
@@ -23455,7 +23455,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P159" t="n">
@@ -23468,7 +23468,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S159" t="inlineStr">
@@ -23513,12 +23513,12 @@
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC159" t="inlineStr">
@@ -23607,7 +23607,7 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>-89</v>
+        <v>-90</v>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
@@ -23661,12 +23661,12 @@
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC160" t="inlineStr">
@@ -23803,12 +23803,12 @@
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC161" t="inlineStr">
@@ -23889,7 +23889,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P162" t="n">
@@ -23902,7 +23902,7 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S162" t="inlineStr">
@@ -23947,12 +23947,12 @@
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC162" t="inlineStr">
@@ -24037,7 +24037,7 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
@@ -24091,12 +24091,12 @@
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC163" t="inlineStr">
@@ -24181,7 +24181,7 @@
         </is>
       </c>
       <c r="P164" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
@@ -24235,12 +24235,12 @@
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC164" t="inlineStr">
@@ -24325,7 +24325,7 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
@@ -24379,12 +24379,12 @@
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC165" t="inlineStr">
@@ -24469,7 +24469,7 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
@@ -24523,12 +24523,12 @@
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC166" t="inlineStr">
@@ -24613,7 +24613,7 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
@@ -24667,12 +24667,12 @@
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC167" t="inlineStr">
@@ -24757,7 +24757,7 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
@@ -24811,12 +24811,12 @@
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC168" t="inlineStr">
@@ -24949,12 +24949,12 @@
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC169" t="inlineStr">
@@ -24993,7 +24993,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>L. &amp; M. L████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>L. &amp; G. J████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -25035,7 +25035,7 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P170" t="n">
@@ -25048,7 +25048,7 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S170" t="inlineStr">
@@ -25093,17 +25093,17 @@
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>L. &amp; M. L████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>L. &amp; G. J████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD170" t="inlineStr">
@@ -25231,12 +25231,12 @@
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC171" t="inlineStr">
@@ -25321,7 +25321,7 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="Q172" t="inlineStr">
         <is>
@@ -25375,12 +25375,12 @@
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC172" t="inlineStr">
@@ -25461,7 +25461,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P173" t="n">
@@ -25474,7 +25474,7 @@
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S173" t="inlineStr">
@@ -25519,12 +25519,12 @@
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC173" t="inlineStr">
@@ -25609,7 +25609,7 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q174" t="inlineStr">
         <is>
@@ -25663,12 +25663,12 @@
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC174" t="inlineStr">
@@ -25749,7 +25749,7 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P175" t="n">
@@ -25762,7 +25762,7 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S175" t="inlineStr">
@@ -25807,12 +25807,12 @@
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC175" t="inlineStr">
@@ -25893,7 +25893,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P176" t="n">
@@ -25906,7 +25906,7 @@
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S176" t="inlineStr">
@@ -25951,12 +25951,12 @@
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC176" t="inlineStr">
@@ -26089,12 +26089,12 @@
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC177" t="inlineStr">
@@ -26183,7 +26183,7 @@
         </is>
       </c>
       <c r="P178" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q178" t="inlineStr">
         <is>
@@ -26237,12 +26237,12 @@
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC178" t="inlineStr">
@@ -26327,7 +26327,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P179" t="n">
@@ -26340,7 +26340,7 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S179" t="inlineStr">
@@ -26385,12 +26385,12 @@
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC179" t="inlineStr">
@@ -26475,7 +26475,7 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q180" t="inlineStr">
         <is>
@@ -26529,12 +26529,12 @@
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC180" t="inlineStr">
@@ -26615,7 +26615,7 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P181" t="n">
@@ -26628,7 +26628,7 @@
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S181" t="inlineStr">
@@ -26673,12 +26673,12 @@
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC181" t="inlineStr">
@@ -26717,7 +26717,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>D. &amp; W. H█████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>M. &amp; J. J████████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -26759,7 +26759,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P182" t="n">
@@ -26772,7 +26772,7 @@
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S182" t="inlineStr">
@@ -26817,17 +26817,17 @@
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>D. &amp; W. H█████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>M. &amp; J. J████████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD182" t="inlineStr">
@@ -26955,12 +26955,12 @@
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC183" t="inlineStr">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P184" t="n">
@@ -27054,7 +27054,7 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S184" t="inlineStr">
@@ -27099,12 +27099,12 @@
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC184" t="inlineStr">
@@ -27193,7 +27193,7 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
@@ -27247,12 +27247,12 @@
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC185" t="inlineStr">
@@ -27345,7 +27345,7 @@
         </is>
       </c>
       <c r="P186" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
@@ -27399,12 +27399,12 @@
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC186" t="inlineStr">
@@ -27489,7 +27489,7 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P187" t="n">
@@ -27502,7 +27502,7 @@
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S187" t="inlineStr">
@@ -27547,12 +27547,12 @@
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC187" t="inlineStr">
@@ -27633,7 +27633,7 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P188" t="inlineStr"/>
@@ -27650,7 +27650,7 @@
       </c>
       <c r="T188" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=26-CA-000549</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=26-CA-000549</t>
         </is>
       </c>
       <c r="U188" t="inlineStr">
@@ -27660,7 +27660,7 @@
       </c>
       <c r="V188" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W188" t="inlineStr">
@@ -27685,12 +27685,12 @@
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC188" t="inlineStr">
@@ -27823,12 +27823,12 @@
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC189" t="inlineStr">
@@ -27913,7 +27913,7 @@
         </is>
       </c>
       <c r="P190" t="n">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="Q190" t="inlineStr">
         <is>
@@ -27967,12 +27967,12 @@
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC190" t="inlineStr">
@@ -28057,7 +28057,7 @@
         </is>
       </c>
       <c r="P191" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q191" t="inlineStr">
         <is>
@@ -28111,12 +28111,12 @@
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC191" t="inlineStr">
@@ -28201,7 +28201,7 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
@@ -28255,12 +28255,12 @@
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC192" t="inlineStr">
@@ -28345,7 +28345,7 @@
         </is>
       </c>
       <c r="P193" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
@@ -28399,12 +28399,12 @@
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC193" t="inlineStr">
@@ -28493,7 +28493,7 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Q194" t="inlineStr">
         <is>
@@ -28547,12 +28547,12 @@
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC194" t="inlineStr">
@@ -28645,7 +28645,7 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
@@ -28699,12 +28699,12 @@
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC195" t="inlineStr">
@@ -28797,7 +28797,7 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
@@ -28851,12 +28851,12 @@
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC196" t="inlineStr">
@@ -28949,7 +28949,7 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Q197" t="inlineStr">
         <is>
@@ -29003,12 +29003,12 @@
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC197" t="inlineStr">
@@ -29051,7 +29051,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>J. &amp; D. S████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>S. &amp; D. D██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -29093,7 +29093,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P198" t="n">
@@ -29106,7 +29106,7 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S198" t="inlineStr">
@@ -29151,17 +29151,17 @@
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC198" t="inlineStr">
         <is>
-          <t>J. &amp; D. S████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>S. &amp; D. D██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD198" t="inlineStr">
@@ -29195,7 +29195,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>J. &amp; L. A███████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>S. &amp; W. W████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -29237,7 +29237,7 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P199" t="n">
@@ -29250,7 +29250,7 @@
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S199" t="inlineStr">
@@ -29295,17 +29295,17 @@
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC199" t="inlineStr">
         <is>
-          <t>J. &amp; L. A███████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>S. &amp; W. W████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD199" t="inlineStr">
@@ -29381,7 +29381,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P200" t="n">
@@ -29394,7 +29394,7 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S200" t="inlineStr">
@@ -29439,12 +29439,12 @@
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC200" t="inlineStr">
@@ -29529,7 +29529,7 @@
         </is>
       </c>
       <c r="P201" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q201" t="inlineStr">
         <is>
@@ -29583,12 +29583,12 @@
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC201" t="inlineStr">
@@ -29669,7 +29669,7 @@
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P202" t="n">
@@ -29682,7 +29682,7 @@
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S202" t="inlineStr">
@@ -29727,12 +29727,12 @@
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC202" t="inlineStr">
@@ -29821,7 +29821,7 @@
         </is>
       </c>
       <c r="P203" t="n">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="Q203" t="inlineStr">
         <is>
@@ -29875,12 +29875,12 @@
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC203" t="inlineStr">
@@ -29969,7 +29969,7 @@
         </is>
       </c>
       <c r="P204" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q204" t="inlineStr">
         <is>
@@ -30023,12 +30023,12 @@
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC204" t="inlineStr">
@@ -30117,7 +30117,7 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Q205" t="inlineStr">
         <is>
@@ -30171,12 +30171,12 @@
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC205" t="inlineStr">
@@ -30265,7 +30265,7 @@
         </is>
       </c>
       <c r="P206" t="n">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="Q206" t="inlineStr">
         <is>
@@ -30319,12 +30319,12 @@
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC206" t="inlineStr">
@@ -30405,7 +30405,7 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P207" t="n">
@@ -30418,7 +30418,7 @@
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S207" t="inlineStr">
@@ -30463,12 +30463,12 @@
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC207" t="inlineStr">
@@ -30549,7 +30549,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P208" t="inlineStr"/>
@@ -30566,7 +30566,7 @@
       </c>
       <c r="T208" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=25-CA-002135</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=25-CA-002135</t>
         </is>
       </c>
       <c r="U208" t="inlineStr">
@@ -30576,7 +30576,7 @@
       </c>
       <c r="V208" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W208" t="inlineStr">
@@ -30601,12 +30601,12 @@
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC208" t="inlineStr">
@@ -30687,7 +30687,7 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P209" t="inlineStr"/>
@@ -30704,7 +30704,7 @@
       </c>
       <c r="T209" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=22-CA-008602</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=22-CA-008602</t>
         </is>
       </c>
       <c r="U209" t="inlineStr">
@@ -30714,7 +30714,7 @@
       </c>
       <c r="V209" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W209" t="inlineStr">
@@ -30739,12 +30739,12 @@
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC209" t="inlineStr">
@@ -30825,7 +30825,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P210" t="n">
@@ -30838,7 +30838,7 @@
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S210" t="inlineStr">
@@ -30883,12 +30883,12 @@
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC210" t="inlineStr">
@@ -30973,7 +30973,7 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q211" t="inlineStr">
         <is>
@@ -31027,12 +31027,12 @@
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC211" t="inlineStr">
@@ -31113,7 +31113,7 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P212" t="n">
@@ -31126,7 +31126,7 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S212" t="inlineStr">
@@ -31171,12 +31171,12 @@
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC212" t="inlineStr">
@@ -31257,7 +31257,7 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P213" t="n">
@@ -31270,7 +31270,7 @@
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S213" t="inlineStr">
@@ -31315,12 +31315,12 @@
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC213" t="inlineStr">
@@ -31405,7 +31405,7 @@
         </is>
       </c>
       <c r="P214" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q214" t="inlineStr">
         <is>
@@ -31459,12 +31459,12 @@
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC214" t="inlineStr">
@@ -31597,12 +31597,12 @@
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC215" t="inlineStr">
@@ -31683,7 +31683,7 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P216" t="n">
@@ -31696,7 +31696,7 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S216" t="inlineStr">
@@ -31741,12 +31741,12 @@
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC216" t="inlineStr">
@@ -31827,7 +31827,7 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P217" t="n">
@@ -31840,7 +31840,7 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S217" t="inlineStr">
@@ -31885,12 +31885,12 @@
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC217" t="inlineStr">
@@ -31979,7 +31979,7 @@
         </is>
       </c>
       <c r="P218" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q218" t="inlineStr">
         <is>
@@ -32033,12 +32033,12 @@
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC218" t="inlineStr">
@@ -32131,7 +32131,7 @@
         </is>
       </c>
       <c r="P219" t="n">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="Q219" t="inlineStr">
         <is>
@@ -32185,12 +32185,12 @@
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC219" t="inlineStr">
@@ -32283,7 +32283,7 @@
         </is>
       </c>
       <c r="P220" t="n">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="Q220" t="inlineStr">
         <is>
@@ -32337,12 +32337,12 @@
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC220" t="inlineStr">
@@ -32479,12 +32479,12 @@
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC221" t="inlineStr">
@@ -32569,7 +32569,7 @@
         </is>
       </c>
       <c r="P222" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q222" t="inlineStr">
         <is>
@@ -32623,12 +32623,12 @@
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC222" t="inlineStr">
@@ -32717,7 +32717,7 @@
         </is>
       </c>
       <c r="P223" t="n">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Q223" t="inlineStr">
         <is>
@@ -32771,12 +32771,12 @@
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC223" t="inlineStr">
@@ -32865,7 +32865,7 @@
         </is>
       </c>
       <c r="P224" t="n">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="Q224" t="inlineStr">
         <is>
@@ -32919,12 +32919,12 @@
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC224" t="inlineStr">
@@ -33013,7 +33013,7 @@
         </is>
       </c>
       <c r="P225" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q225" t="inlineStr">
         <is>
@@ -33067,12 +33067,12 @@
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC225" t="inlineStr">
@@ -33161,7 +33161,7 @@
         </is>
       </c>
       <c r="P226" t="n">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="Q226" t="inlineStr">
         <is>
@@ -33215,12 +33215,12 @@
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC226" t="inlineStr">
@@ -33305,7 +33305,7 @@
         </is>
       </c>
       <c r="P227" t="n">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="Q227" t="inlineStr">
         <is>
@@ -33359,12 +33359,12 @@
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC227" t="inlineStr">
@@ -33497,12 +33497,12 @@
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC228" t="inlineStr">
@@ -33587,7 +33587,7 @@
         </is>
       </c>
       <c r="P229" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q229" t="inlineStr">
         <is>
@@ -33641,12 +33641,12 @@
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC229" t="inlineStr">
@@ -33735,7 +33735,7 @@
         </is>
       </c>
       <c r="P230" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q230" t="inlineStr">
         <is>
@@ -33789,12 +33789,12 @@
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC230" t="inlineStr">
@@ -33879,7 +33879,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P231" t="n">
@@ -33892,7 +33892,7 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S231" t="inlineStr">
@@ -33937,12 +33937,12 @@
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC231" t="inlineStr">
@@ -34031,7 +34031,7 @@
         </is>
       </c>
       <c r="P232" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q232" t="inlineStr">
         <is>
@@ -34085,12 +34085,12 @@
       </c>
       <c r="AA232" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC232" t="inlineStr">
@@ -34183,7 +34183,7 @@
         </is>
       </c>
       <c r="P233" t="n">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q233" t="inlineStr">
         <is>
@@ -34237,12 +34237,12 @@
       </c>
       <c r="AA233" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC233" t="inlineStr">
@@ -34379,12 +34379,12 @@
       </c>
       <c r="AA234" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC234" t="inlineStr">
@@ -34465,7 +34465,7 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P235" t="inlineStr"/>
@@ -34482,7 +34482,7 @@
       </c>
       <c r="T235" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=26-CA-007844</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=26-CA-007844</t>
         </is>
       </c>
       <c r="U235" t="inlineStr">
@@ -34492,7 +34492,7 @@
       </c>
       <c r="V235" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W235" t="inlineStr">
@@ -34517,12 +34517,12 @@
       </c>
       <c r="AA235" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB235" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC235" t="inlineStr">
@@ -34611,7 +34611,7 @@
         </is>
       </c>
       <c r="P236" t="n">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="Q236" t="inlineStr">
         <is>
@@ -34665,12 +34665,12 @@
       </c>
       <c r="AA236" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC236" t="inlineStr">
@@ -34763,7 +34763,7 @@
         </is>
       </c>
       <c r="P237" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q237" t="inlineStr">
         <is>
@@ -34817,12 +34817,12 @@
       </c>
       <c r="AA237" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC237" t="inlineStr">
@@ -34915,7 +34915,7 @@
         </is>
       </c>
       <c r="P238" t="n">
-        <v>-115</v>
+        <v>-116</v>
       </c>
       <c r="Q238" t="inlineStr">
         <is>
@@ -34969,12 +34969,12 @@
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB238" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC238" t="inlineStr">
@@ -35067,7 +35067,7 @@
         </is>
       </c>
       <c r="P239" t="n">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="Q239" t="inlineStr">
         <is>
@@ -35121,12 +35121,12 @@
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB239" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC239" t="inlineStr">
@@ -35211,7 +35211,7 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P240" t="inlineStr"/>
@@ -35228,7 +35228,7 @@
       </c>
       <c r="T240" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=18-CA-007512</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=18-CA-007512</t>
         </is>
       </c>
       <c r="U240" t="inlineStr">
@@ -35238,7 +35238,7 @@
       </c>
       <c r="V240" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W240" t="inlineStr">
@@ -35263,12 +35263,12 @@
       </c>
       <c r="AA240" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB240" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC240" t="inlineStr">
@@ -35307,7 +35307,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>D. &amp; L. S██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>E. &amp; N. S██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -35349,7 +35349,7 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P241" t="n">
@@ -35362,7 +35362,7 @@
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S241" t="inlineStr">
@@ -35407,17 +35407,17 @@
       </c>
       <c r="AA241" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB241" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC241" t="inlineStr">
         <is>
-          <t>D. &amp; L. S██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>E. &amp; N. S██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD241" t="inlineStr">
@@ -35497,7 +35497,7 @@
         </is>
       </c>
       <c r="P242" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q242" t="inlineStr">
         <is>
@@ -35551,12 +35551,12 @@
       </c>
       <c r="AA242" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC242" t="inlineStr">
@@ -35689,12 +35689,12 @@
       </c>
       <c r="AA243" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC243" t="inlineStr">
@@ -35779,7 +35779,7 @@
         </is>
       </c>
       <c r="P244" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q244" t="inlineStr">
         <is>
@@ -35833,12 +35833,12 @@
       </c>
       <c r="AA244" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC244" t="inlineStr">
@@ -35877,7 +35877,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>K. &amp; G. G█████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>F. &amp; G. T████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -35919,7 +35919,7 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P245" t="n">
@@ -35932,7 +35932,7 @@
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S245" t="inlineStr">
@@ -35977,17 +35977,17 @@
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC245" t="inlineStr">
         <is>
-          <t>K. &amp; G. G█████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>F. &amp; G. T████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD245" t="inlineStr">
@@ -36067,7 +36067,7 @@
         </is>
       </c>
       <c r="P246" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q246" t="inlineStr">
         <is>
@@ -36121,12 +36121,12 @@
       </c>
       <c r="AA246" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC246" t="inlineStr">
@@ -36211,7 +36211,7 @@
         </is>
       </c>
       <c r="P247" t="n">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Q247" t="inlineStr">
         <is>
@@ -36265,12 +36265,12 @@
       </c>
       <c r="AA247" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC247" t="inlineStr">
@@ -36359,7 +36359,7 @@
         </is>
       </c>
       <c r="P248" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q248" t="inlineStr">
         <is>
@@ -36413,12 +36413,12 @@
       </c>
       <c r="AA248" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC248" t="inlineStr">
@@ -36507,7 +36507,7 @@
         </is>
       </c>
       <c r="P249" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q249" t="inlineStr">
         <is>
@@ -36561,12 +36561,12 @@
       </c>
       <c r="AA249" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC249" t="inlineStr">
@@ -36655,7 +36655,7 @@
         </is>
       </c>
       <c r="P250" t="n">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="Q250" t="inlineStr">
         <is>
@@ -36709,12 +36709,12 @@
       </c>
       <c r="AA250" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB250" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC250" t="inlineStr">
@@ -36757,7 +36757,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>H. &amp; S. S██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>D. &amp; S. S██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -36799,7 +36799,7 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P251" t="n">
@@ -36812,7 +36812,7 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S251" t="inlineStr">
@@ -36857,17 +36857,17 @@
       </c>
       <c r="AA251" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB251" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC251" t="inlineStr">
         <is>
-          <t>H. &amp; S. S██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>D. &amp; S. S██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD251" t="inlineStr">
@@ -36943,7 +36943,7 @@
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P252" t="n">
@@ -36956,7 +36956,7 @@
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S252" t="inlineStr">
@@ -37001,12 +37001,12 @@
       </c>
       <c r="AA252" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB252" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC252" t="inlineStr">
@@ -37091,7 +37091,7 @@
         </is>
       </c>
       <c r="P253" t="n">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="Q253" t="inlineStr">
         <is>
@@ -37145,12 +37145,12 @@
       </c>
       <c r="AA253" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB253" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC253" t="inlineStr">
@@ -37239,7 +37239,7 @@
         </is>
       </c>
       <c r="P254" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q254" t="inlineStr">
         <is>
@@ -37293,12 +37293,12 @@
       </c>
       <c r="AA254" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB254" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC254" t="inlineStr">
@@ -37341,7 +37341,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>R. &amp; R. R██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>K. &amp; R. N████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -37383,7 +37383,7 @@
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P255" t="n">
@@ -37396,7 +37396,7 @@
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S255" t="inlineStr">
@@ -37441,17 +37441,17 @@
       </c>
       <c r="AA255" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB255" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC255" t="inlineStr">
         <is>
-          <t>R. &amp; R. R██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>K. &amp; R. N████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD255" t="inlineStr">
@@ -37535,7 +37535,7 @@
         </is>
       </c>
       <c r="P256" t="n">
-        <v>-89</v>
+        <v>-90</v>
       </c>
       <c r="Q256" t="inlineStr">
         <is>
@@ -37589,12 +37589,12 @@
       </c>
       <c r="AA256" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB256" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC256" t="inlineStr">
@@ -37687,7 +37687,7 @@
         </is>
       </c>
       <c r="P257" t="n">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="Q257" t="inlineStr">
         <is>
@@ -37741,12 +37741,12 @@
       </c>
       <c r="AA257" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB257" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC257" t="inlineStr">
@@ -37839,7 +37839,7 @@
         </is>
       </c>
       <c r="P258" t="n">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="Q258" t="inlineStr">
         <is>
@@ -37893,12 +37893,12 @@
       </c>
       <c r="AA258" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB258" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC258" t="inlineStr">
@@ -37991,7 +37991,7 @@
         </is>
       </c>
       <c r="P259" t="n">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="Q259" t="inlineStr">
         <is>
@@ -38045,12 +38045,12 @@
       </c>
       <c r="AA259" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB259" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC259" t="inlineStr">
@@ -38143,7 +38143,7 @@
         </is>
       </c>
       <c r="P260" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q260" t="inlineStr">
         <is>
@@ -38197,12 +38197,12 @@
       </c>
       <c r="AA260" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB260" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC260" t="inlineStr">
@@ -38245,7 +38245,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>C. &amp; V. C████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>V. &amp; C. V███████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -38287,7 +38287,7 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P261" t="n">
@@ -38300,7 +38300,7 @@
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S261" t="inlineStr">
@@ -38345,17 +38345,17 @@
       </c>
       <c r="AA261" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB261" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC261" t="inlineStr">
         <is>
-          <t>C. &amp; V. C████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>V. &amp; C. V███████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD261" t="inlineStr">
@@ -38431,7 +38431,7 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P262" t="n">
@@ -38444,7 +38444,7 @@
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S262" t="inlineStr">
@@ -38489,12 +38489,12 @@
       </c>
       <c r="AA262" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB262" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC262" t="inlineStr">
@@ -38627,12 +38627,12 @@
       </c>
       <c r="AA263" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB263" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC263" t="inlineStr">
@@ -38725,7 +38725,7 @@
         </is>
       </c>
       <c r="P264" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Q264" t="inlineStr">
         <is>
@@ -38779,12 +38779,12 @@
       </c>
       <c r="AA264" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB264" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC264" t="inlineStr">
@@ -38877,7 +38877,7 @@
         </is>
       </c>
       <c r="P265" t="n">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="Q265" t="inlineStr">
         <is>
@@ -38931,12 +38931,12 @@
       </c>
       <c r="AA265" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB265" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC265" t="inlineStr">
@@ -39025,7 +39025,7 @@
         </is>
       </c>
       <c r="P266" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q266" t="inlineStr">
         <is>
@@ -39079,12 +39079,12 @@
       </c>
       <c r="AA266" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB266" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC266" t="inlineStr">
@@ -39217,12 +39217,12 @@
       </c>
       <c r="AA267" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB267" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC267" t="inlineStr">
@@ -39311,7 +39311,7 @@
         </is>
       </c>
       <c r="P268" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q268" t="inlineStr">
         <is>
@@ -39365,12 +39365,12 @@
       </c>
       <c r="AA268" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB268" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC268" t="inlineStr">
@@ -39459,7 +39459,7 @@
         </is>
       </c>
       <c r="P269" t="n">
-        <v>-150</v>
+        <v>-151</v>
       </c>
       <c r="Q269" t="inlineStr">
         <is>
@@ -39513,12 +39513,12 @@
       </c>
       <c r="AA269" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB269" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC269" t="inlineStr">
@@ -39611,7 +39611,7 @@
         </is>
       </c>
       <c r="P270" t="n">
-        <v>-52</v>
+        <v>-53</v>
       </c>
       <c r="Q270" t="inlineStr">
         <is>
@@ -39665,12 +39665,12 @@
       </c>
       <c r="AA270" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB270" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC270" t="inlineStr">
@@ -39807,12 +39807,12 @@
       </c>
       <c r="AA271" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB271" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC271" t="inlineStr">
@@ -39897,7 +39897,7 @@
         </is>
       </c>
       <c r="P272" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q272" t="inlineStr">
         <is>
@@ -39951,12 +39951,12 @@
       </c>
       <c r="AA272" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC272" t="inlineStr">
@@ -40041,7 +40041,7 @@
         </is>
       </c>
       <c r="P273" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q273" t="inlineStr">
         <is>
@@ -40095,12 +40095,12 @@
       </c>
       <c r="AA273" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC273" t="inlineStr">
@@ -40189,7 +40189,7 @@
         </is>
       </c>
       <c r="P274" t="n">
-        <v>-89</v>
+        <v>-90</v>
       </c>
       <c r="Q274" t="inlineStr">
         <is>
@@ -40243,12 +40243,12 @@
       </c>
       <c r="AA274" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC274" t="inlineStr">
@@ -40333,7 +40333,7 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P275" t="inlineStr"/>
@@ -40350,7 +40350,7 @@
       </c>
       <c r="T275" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=09-CA-009881</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=09-CA-009881</t>
         </is>
       </c>
       <c r="U275" t="inlineStr">
@@ -40360,7 +40360,7 @@
       </c>
       <c r="V275" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W275" t="inlineStr">
@@ -40385,12 +40385,12 @@
       </c>
       <c r="AA275" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC275" t="inlineStr">
@@ -40479,7 +40479,7 @@
         </is>
       </c>
       <c r="P276" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q276" t="inlineStr">
         <is>
@@ -40533,12 +40533,12 @@
       </c>
       <c r="AA276" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC276" t="inlineStr">
@@ -40631,7 +40631,7 @@
         </is>
       </c>
       <c r="P277" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q277" t="inlineStr">
         <is>
@@ -40685,12 +40685,12 @@
       </c>
       <c r="AA277" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB277" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC277" t="inlineStr">
@@ -40775,7 +40775,7 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P278" t="n">
@@ -40788,7 +40788,7 @@
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S278" t="inlineStr">
@@ -40833,12 +40833,12 @@
       </c>
       <c r="AA278" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB278" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC278" t="inlineStr">
@@ -40919,7 +40919,7 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P279" t="n">
@@ -40932,7 +40932,7 @@
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S279" t="inlineStr">
@@ -40977,12 +40977,12 @@
       </c>
       <c r="AA279" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB279" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC279" t="inlineStr">
@@ -41071,7 +41071,7 @@
         </is>
       </c>
       <c r="P280" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Q280" t="inlineStr">
         <is>
@@ -41125,12 +41125,12 @@
       </c>
       <c r="AA280" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB280" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC280" t="inlineStr">
@@ -41215,7 +41215,7 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P281" t="n">
@@ -41228,7 +41228,7 @@
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S281" t="inlineStr">
@@ -41273,12 +41273,12 @@
       </c>
       <c r="AA281" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB281" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC281" t="inlineStr">
@@ -41367,7 +41367,7 @@
         </is>
       </c>
       <c r="P282" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q282" t="inlineStr">
         <is>
@@ -41421,12 +41421,12 @@
       </c>
       <c r="AA282" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB282" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC282" t="inlineStr">
@@ -41519,7 +41519,7 @@
         </is>
       </c>
       <c r="P283" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q283" t="inlineStr">
         <is>
@@ -41573,12 +41573,12 @@
       </c>
       <c r="AA283" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB283" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC283" t="inlineStr">
@@ -41671,7 +41671,7 @@
         </is>
       </c>
       <c r="P284" t="n">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="Q284" t="inlineStr">
         <is>
@@ -41725,12 +41725,12 @@
       </c>
       <c r="AA284" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB284" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC284" t="inlineStr">
@@ -41815,7 +41815,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P285" t="n">
@@ -41828,7 +41828,7 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S285" t="inlineStr">
@@ -41873,12 +41873,12 @@
       </c>
       <c r="AA285" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB285" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC285" t="inlineStr">
@@ -41959,7 +41959,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P286" t="inlineStr"/>
@@ -41976,7 +41976,7 @@
       </c>
       <c r="T286" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=24-CA-000685</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=24-CA-000685</t>
         </is>
       </c>
       <c r="U286" t="inlineStr">
@@ -41986,7 +41986,7 @@
       </c>
       <c r="V286" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W286" t="inlineStr">
@@ -42011,12 +42011,12 @@
       </c>
       <c r="AA286" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB286" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC286" t="inlineStr">
@@ -42105,7 +42105,7 @@
         </is>
       </c>
       <c r="P287" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q287" t="inlineStr">
         <is>
@@ -42159,12 +42159,12 @@
       </c>
       <c r="AA287" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB287" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC287" t="inlineStr">
@@ -42257,7 +42257,7 @@
         </is>
       </c>
       <c r="P288" t="n">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="Q288" t="inlineStr">
         <is>
@@ -42311,12 +42311,12 @@
       </c>
       <c r="AA288" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB288" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC288" t="inlineStr">
@@ -42401,7 +42401,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P289" t="n">
@@ -42414,7 +42414,7 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S289" t="inlineStr">
@@ -42459,12 +42459,12 @@
       </c>
       <c r="AA289" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB289" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC289" t="inlineStr">
@@ -42553,7 +42553,7 @@
         </is>
       </c>
       <c r="P290" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q290" t="inlineStr">
         <is>
@@ -42607,12 +42607,12 @@
       </c>
       <c r="AA290" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB290" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC290" t="inlineStr">
@@ -42697,7 +42697,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P291" t="n">
@@ -42710,7 +42710,7 @@
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S291" t="inlineStr">
@@ -42755,12 +42755,12 @@
       </c>
       <c r="AA291" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB291" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC291" t="inlineStr">
@@ -42849,7 +42849,7 @@
         </is>
       </c>
       <c r="P292" t="n">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="Q292" t="inlineStr">
         <is>
@@ -42903,12 +42903,12 @@
       </c>
       <c r="AA292" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB292" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC292" t="inlineStr">
@@ -43001,7 +43001,7 @@
         </is>
       </c>
       <c r="P293" t="n">
-        <v>-52</v>
+        <v>-53</v>
       </c>
       <c r="Q293" t="inlineStr">
         <is>
@@ -43055,12 +43055,12 @@
       </c>
       <c r="AA293" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB293" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC293" t="inlineStr">
@@ -43197,12 +43197,12 @@
       </c>
       <c r="AA294" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB294" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC294" t="inlineStr">
@@ -43291,7 +43291,7 @@
         </is>
       </c>
       <c r="P295" t="n">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="Q295" t="inlineStr">
         <is>
@@ -43345,12 +43345,12 @@
       </c>
       <c r="AA295" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB295" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC295" t="inlineStr">
@@ -43435,7 +43435,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P296" t="n">
@@ -43448,7 +43448,7 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S296" t="inlineStr">
@@ -43493,12 +43493,12 @@
       </c>
       <c r="AA296" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB296" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC296" t="inlineStr">
@@ -43587,7 +43587,7 @@
         </is>
       </c>
       <c r="P297" t="n">
-        <v>-89</v>
+        <v>-90</v>
       </c>
       <c r="Q297" t="inlineStr">
         <is>
@@ -43641,12 +43641,12 @@
       </c>
       <c r="AA297" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB297" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC297" t="inlineStr">
@@ -43731,7 +43731,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P298" t="inlineStr"/>
@@ -43748,7 +43748,7 @@
       </c>
       <c r="T298" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=24-CA-005012</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=24-CA-005012</t>
         </is>
       </c>
       <c r="U298" t="inlineStr">
@@ -43758,7 +43758,7 @@
       </c>
       <c r="V298" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W298" t="inlineStr">
@@ -43783,12 +43783,12 @@
       </c>
       <c r="AA298" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB298" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC298" t="inlineStr">
@@ -43877,7 +43877,7 @@
         </is>
       </c>
       <c r="P299" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q299" t="inlineStr">
         <is>
@@ -43931,12 +43931,12 @@
       </c>
       <c r="AA299" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC299" t="inlineStr">
@@ -44025,7 +44025,7 @@
         </is>
       </c>
       <c r="P300" t="n">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="Q300" t="inlineStr">
         <is>
@@ -44079,12 +44079,12 @@
       </c>
       <c r="AA300" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB300" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC300" t="inlineStr">
@@ -44217,12 +44217,12 @@
       </c>
       <c r="AA301" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB301" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC301" t="inlineStr">
@@ -44315,7 +44315,7 @@
         </is>
       </c>
       <c r="P302" t="n">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="Q302" t="inlineStr">
         <is>
@@ -44369,12 +44369,12 @@
       </c>
       <c r="AA302" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB302" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC302" t="inlineStr">
@@ -44463,7 +44463,7 @@
         </is>
       </c>
       <c r="P303" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q303" t="inlineStr">
         <is>
@@ -44517,12 +44517,12 @@
       </c>
       <c r="AA303" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB303" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC303" t="inlineStr">
@@ -44611,7 +44611,7 @@
         </is>
       </c>
       <c r="P304" t="n">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="Q304" t="inlineStr">
         <is>
@@ -44665,12 +44665,12 @@
       </c>
       <c r="AA304" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB304" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC304" t="inlineStr">
@@ -44807,12 +44807,12 @@
       </c>
       <c r="AA305" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB305" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC305" t="inlineStr">
@@ -44901,7 +44901,7 @@
         </is>
       </c>
       <c r="P306" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q306" t="inlineStr">
         <is>
@@ -44955,12 +44955,12 @@
       </c>
       <c r="AA306" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB306" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC306" t="inlineStr">
@@ -45053,7 +45053,7 @@
         </is>
       </c>
       <c r="P307" t="n">
-        <v>-89</v>
+        <v>-90</v>
       </c>
       <c r="Q307" t="inlineStr">
         <is>
@@ -45107,12 +45107,12 @@
       </c>
       <c r="AA307" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB307" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC307" t="inlineStr">
@@ -45155,7 +45155,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>F. &amp; H. T████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>L. &amp; E. T████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -45197,7 +45197,7 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P308" t="n">
@@ -45210,7 +45210,7 @@
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S308" t="inlineStr">
@@ -45255,17 +45255,17 @@
       </c>
       <c r="AA308" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC308" t="inlineStr">
         <is>
-          <t>F. &amp; H. T████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>L. &amp; E. T████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD308" t="inlineStr">
@@ -45345,7 +45345,7 @@
         </is>
       </c>
       <c r="P309" t="n">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Q309" t="inlineStr">
         <is>
@@ -45399,12 +45399,12 @@
       </c>
       <c r="AA309" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB309" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC309" t="inlineStr">
@@ -45489,7 +45489,7 @@
         </is>
       </c>
       <c r="P310" t="n">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="Q310" t="inlineStr">
         <is>
@@ -45543,12 +45543,12 @@
       </c>
       <c r="AA310" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB310" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC310" t="inlineStr">
@@ -45633,7 +45633,7 @@
         </is>
       </c>
       <c r="P311" t="n">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q311" t="inlineStr">
         <is>
@@ -45687,12 +45687,12 @@
       </c>
       <c r="AA311" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC311" t="inlineStr">
@@ -45731,7 +45731,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>L. &amp; G. D████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>D. &amp; M. D████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -45773,7 +45773,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P312" t="n">
@@ -45786,7 +45786,7 @@
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S312" t="inlineStr">
@@ -45831,17 +45831,17 @@
       </c>
       <c r="AA312" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC312" t="inlineStr">
         <is>
-          <t>L. &amp; G. D████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>D. &amp; M. D████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD312" t="inlineStr">
@@ -45925,7 +45925,7 @@
         </is>
       </c>
       <c r="P313" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q313" t="inlineStr">
         <is>
@@ -45979,12 +45979,12 @@
       </c>
       <c r="AA313" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB313" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC313" t="inlineStr">
@@ -46073,7 +46073,7 @@
         </is>
       </c>
       <c r="P314" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q314" t="inlineStr">
         <is>
@@ -46127,12 +46127,12 @@
       </c>
       <c r="AA314" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB314" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC314" t="inlineStr">
@@ -46221,7 +46221,7 @@
         </is>
       </c>
       <c r="P315" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q315" t="inlineStr">
         <is>
@@ -46275,12 +46275,12 @@
       </c>
       <c r="AA315" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB315" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC315" t="inlineStr">
@@ -46373,7 +46373,7 @@
         </is>
       </c>
       <c r="P316" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q316" t="inlineStr">
         <is>
@@ -46427,12 +46427,12 @@
       </c>
       <c r="AA316" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB316" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC316" t="inlineStr">
@@ -46517,7 +46517,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P317" t="n">
@@ -46530,7 +46530,7 @@
       </c>
       <c r="R317" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S317" t="inlineStr">
@@ -46575,12 +46575,12 @@
       </c>
       <c r="AA317" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB317" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC317" t="inlineStr">
@@ -46669,7 +46669,7 @@
         </is>
       </c>
       <c r="P318" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q318" t="inlineStr">
         <is>
@@ -46723,12 +46723,12 @@
       </c>
       <c r="AA318" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB318" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC318" t="inlineStr">
@@ -46821,7 +46821,7 @@
         </is>
       </c>
       <c r="P319" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q319" t="inlineStr">
         <is>
@@ -46875,12 +46875,12 @@
       </c>
       <c r="AA319" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB319" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC319" t="inlineStr">
@@ -46969,7 +46969,7 @@
         </is>
       </c>
       <c r="P320" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q320" t="inlineStr">
         <is>
@@ -47023,12 +47023,12 @@
       </c>
       <c r="AA320" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB320" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC320" t="inlineStr">
@@ -47117,7 +47117,7 @@
         </is>
       </c>
       <c r="P321" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q321" t="inlineStr">
         <is>
@@ -47171,12 +47171,12 @@
       </c>
       <c r="AA321" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB321" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC321" t="inlineStr">
@@ -47269,7 +47269,7 @@
         </is>
       </c>
       <c r="P322" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q322" t="inlineStr">
         <is>
@@ -47323,12 +47323,12 @@
       </c>
       <c r="AA322" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB322" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC322" t="inlineStr">
@@ -47421,7 +47421,7 @@
         </is>
       </c>
       <c r="P323" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q323" t="inlineStr">
         <is>
@@ -47475,12 +47475,12 @@
       </c>
       <c r="AA323" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB323" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC323" t="inlineStr">
@@ -47573,7 +47573,7 @@
         </is>
       </c>
       <c r="P324" t="n">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q324" t="inlineStr">
         <is>
@@ -47627,12 +47627,12 @@
       </c>
       <c r="AA324" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB324" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC324" t="inlineStr">
@@ -47717,7 +47717,7 @@
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P325" t="n">
@@ -47730,7 +47730,7 @@
       </c>
       <c r="R325" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S325" t="inlineStr">
@@ -47775,12 +47775,12 @@
       </c>
       <c r="AA325" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB325" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC325" t="inlineStr">
@@ -47869,7 +47869,7 @@
         </is>
       </c>
       <c r="P326" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q326" t="inlineStr">
         <is>
@@ -47923,12 +47923,12 @@
       </c>
       <c r="AA326" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB326" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC326" t="inlineStr">
@@ -48021,7 +48021,7 @@
         </is>
       </c>
       <c r="P327" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q327" t="inlineStr">
         <is>
@@ -48075,12 +48075,12 @@
       </c>
       <c r="AA327" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB327" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC327" t="inlineStr">
@@ -48165,7 +48165,7 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P328" t="n">
@@ -48178,7 +48178,7 @@
       </c>
       <c r="R328" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S328" t="inlineStr">
@@ -48223,12 +48223,12 @@
       </c>
       <c r="AA328" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB328" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC328" t="inlineStr">
@@ -48313,7 +48313,7 @@
         </is>
       </c>
       <c r="P329" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q329" t="inlineStr">
         <is>
@@ -48367,12 +48367,12 @@
       </c>
       <c r="AA329" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB329" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC329" t="inlineStr">
@@ -48457,7 +48457,7 @@
         </is>
       </c>
       <c r="P330" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q330" t="inlineStr">
         <is>
@@ -48511,12 +48511,12 @@
       </c>
       <c r="AA330" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB330" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC330" t="inlineStr">
@@ -48555,7 +48555,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>M. &amp; A. G████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>D. &amp; M. W███████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
@@ -48597,7 +48597,7 @@
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P331" t="n">
@@ -48610,7 +48610,7 @@
       </c>
       <c r="R331" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S331" t="inlineStr">
@@ -48655,17 +48655,17 @@
       </c>
       <c r="AA331" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB331" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC331" t="inlineStr">
         <is>
-          <t>M. &amp; A. G████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>D. &amp; M. W███████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD331" t="inlineStr">
@@ -48745,7 +48745,7 @@
         </is>
       </c>
       <c r="P332" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q332" t="inlineStr">
         <is>
@@ -48799,12 +48799,12 @@
       </c>
       <c r="AA332" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB332" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC332" t="inlineStr">
@@ -48889,7 +48889,7 @@
         </is>
       </c>
       <c r="P333" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q333" t="inlineStr">
         <is>
@@ -48943,12 +48943,12 @@
       </c>
       <c r="AA333" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB333" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC333" t="inlineStr">
@@ -49037,7 +49037,7 @@
         </is>
       </c>
       <c r="P334" t="n">
-        <v>-89</v>
+        <v>-90</v>
       </c>
       <c r="Q334" t="inlineStr">
         <is>
@@ -49091,12 +49091,12 @@
       </c>
       <c r="AA334" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB334" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC334" t="inlineStr">
@@ -49189,7 +49189,7 @@
         </is>
       </c>
       <c r="P335" t="n">
-        <v>-89</v>
+        <v>-90</v>
       </c>
       <c r="Q335" t="inlineStr">
         <is>
@@ -49243,12 +49243,12 @@
       </c>
       <c r="AA335" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB335" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC335" t="inlineStr">
@@ -49333,7 +49333,7 @@
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P336" t="inlineStr"/>
@@ -49350,7 +49350,7 @@
       </c>
       <c r="T336" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=23-CA-000671</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=23-CA-000671</t>
         </is>
       </c>
       <c r="U336" t="inlineStr">
@@ -49360,7 +49360,7 @@
       </c>
       <c r="V336" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W336" t="inlineStr">
@@ -49385,12 +49385,12 @@
       </c>
       <c r="AA336" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB336" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC336" t="inlineStr">
@@ -49479,7 +49479,7 @@
         </is>
       </c>
       <c r="P337" t="n">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="Q337" t="inlineStr">
         <is>
@@ -49533,12 +49533,12 @@
       </c>
       <c r="AA337" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB337" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC337" t="inlineStr">
@@ -49631,7 +49631,7 @@
         </is>
       </c>
       <c r="P338" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q338" t="inlineStr">
         <is>
@@ -49685,12 +49685,12 @@
       </c>
       <c r="AA338" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB338" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC338" t="inlineStr">
@@ -49775,7 +49775,7 @@
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P339" t="n">
@@ -49788,7 +49788,7 @@
       </c>
       <c r="R339" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S339" t="inlineStr">
@@ -49833,12 +49833,12 @@
       </c>
       <c r="AA339" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB339" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC339" t="inlineStr">
@@ -49927,7 +49927,7 @@
         </is>
       </c>
       <c r="P340" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q340" t="inlineStr">
         <is>
@@ -49981,12 +49981,12 @@
       </c>
       <c r="AA340" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB340" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC340" t="inlineStr">
@@ -50079,7 +50079,7 @@
         </is>
       </c>
       <c r="P341" t="n">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="Q341" t="inlineStr">
         <is>
@@ -50133,12 +50133,12 @@
       </c>
       <c r="AA341" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB341" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC341" t="inlineStr">
@@ -50227,7 +50227,7 @@
         </is>
       </c>
       <c r="P342" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q342" t="inlineStr">
         <is>
@@ -50281,12 +50281,12 @@
       </c>
       <c r="AA342" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB342" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC342" t="inlineStr">
@@ -50375,7 +50375,7 @@
         </is>
       </c>
       <c r="P343" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q343" t="inlineStr">
         <is>
@@ -50429,12 +50429,12 @@
       </c>
       <c r="AA343" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB343" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC343" t="inlineStr">
@@ -50527,7 +50527,7 @@
         </is>
       </c>
       <c r="P344" t="n">
-        <v>-52</v>
+        <v>-53</v>
       </c>
       <c r="Q344" t="inlineStr">
         <is>
@@ -50581,12 +50581,12 @@
       </c>
       <c r="AA344" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB344" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC344" t="inlineStr">
@@ -50679,7 +50679,7 @@
         </is>
       </c>
       <c r="P345" t="n">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="Q345" t="inlineStr">
         <is>
@@ -50733,12 +50733,12 @@
       </c>
       <c r="AA345" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB345" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC345" t="inlineStr">
@@ -50831,7 +50831,7 @@
         </is>
       </c>
       <c r="P346" t="n">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="Q346" t="inlineStr">
         <is>
@@ -50885,12 +50885,12 @@
       </c>
       <c r="AA346" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB346" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC346" t="inlineStr">
@@ -50983,7 +50983,7 @@
         </is>
       </c>
       <c r="P347" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q347" t="inlineStr">
         <is>
@@ -51037,12 +51037,12 @@
       </c>
       <c r="AA347" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB347" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC347" t="inlineStr">
@@ -51135,7 +51135,7 @@
         </is>
       </c>
       <c r="P348" t="n">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="Q348" t="inlineStr">
         <is>
@@ -51189,12 +51189,12 @@
       </c>
       <c r="AA348" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB348" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC348" t="inlineStr">
@@ -51287,7 +51287,7 @@
         </is>
       </c>
       <c r="P349" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q349" t="inlineStr">
         <is>
@@ -51341,12 +51341,12 @@
       </c>
       <c r="AA349" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB349" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC349" t="inlineStr">
@@ -51439,7 +51439,7 @@
         </is>
       </c>
       <c r="P350" t="n">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="Q350" t="inlineStr">
         <is>
@@ -51493,12 +51493,12 @@
       </c>
       <c r="AA350" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB350" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC350" t="inlineStr">
@@ -51591,7 +51591,7 @@
         </is>
       </c>
       <c r="P351" t="n">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="Q351" t="inlineStr">
         <is>
@@ -51645,12 +51645,12 @@
       </c>
       <c r="AA351" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB351" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC351" t="inlineStr">
@@ -51743,7 +51743,7 @@
         </is>
       </c>
       <c r="P352" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q352" t="inlineStr">
         <is>
@@ -51797,12 +51797,12 @@
       </c>
       <c r="AA352" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB352" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC352" t="inlineStr">
@@ -51895,7 +51895,7 @@
         </is>
       </c>
       <c r="P353" t="n">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="Q353" t="inlineStr">
         <is>
@@ -51949,12 +51949,12 @@
       </c>
       <c r="AA353" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB353" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC353" t="inlineStr">
@@ -52047,7 +52047,7 @@
         </is>
       </c>
       <c r="P354" t="n">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="Q354" t="inlineStr">
         <is>
@@ -52101,12 +52101,12 @@
       </c>
       <c r="AA354" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB354" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC354" t="inlineStr">
@@ -52191,7 +52191,7 @@
       </c>
       <c r="O355" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P355" t="inlineStr"/>
@@ -52208,7 +52208,7 @@
       </c>
       <c r="T355" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=22-CA-007538</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=22-CA-007538</t>
         </is>
       </c>
       <c r="U355" t="inlineStr">
@@ -52218,7 +52218,7 @@
       </c>
       <c r="V355" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W355" t="inlineStr">
@@ -52243,12 +52243,12 @@
       </c>
       <c r="AA355" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB355" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC355" t="inlineStr">
@@ -52333,7 +52333,7 @@
         </is>
       </c>
       <c r="P356" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q356" t="inlineStr">
         <is>
@@ -52387,12 +52387,12 @@
       </c>
       <c r="AA356" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB356" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC356" t="inlineStr">
@@ -52481,7 +52481,7 @@
         </is>
       </c>
       <c r="P357" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q357" t="inlineStr">
         <is>
@@ -52535,12 +52535,12 @@
       </c>
       <c r="AA357" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB357" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC357" t="inlineStr">
@@ -52633,7 +52633,7 @@
         </is>
       </c>
       <c r="P358" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q358" t="inlineStr">
         <is>
@@ -52687,12 +52687,12 @@
       </c>
       <c r="AA358" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB358" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC358" t="inlineStr">
@@ -52781,7 +52781,7 @@
         </is>
       </c>
       <c r="P359" t="n">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="Q359" t="inlineStr">
         <is>
@@ -52835,12 +52835,12 @@
       </c>
       <c r="AA359" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB359" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC359" t="inlineStr">
@@ -52921,7 +52921,7 @@
       </c>
       <c r="O360" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P360" t="n">
@@ -52934,7 +52934,7 @@
       </c>
       <c r="R360" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S360" t="inlineStr">
@@ -52979,12 +52979,12 @@
       </c>
       <c r="AA360" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB360" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC360" t="inlineStr">
@@ -53073,7 +53073,7 @@
         </is>
       </c>
       <c r="P361" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q361" t="inlineStr">
         <is>
@@ -53127,12 +53127,12 @@
       </c>
       <c r="AA361" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB361" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC361" t="inlineStr">
@@ -53269,12 +53269,12 @@
       </c>
       <c r="AA362" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB362" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC362" t="inlineStr">
@@ -53359,7 +53359,7 @@
         </is>
       </c>
       <c r="P363" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q363" t="inlineStr">
         <is>
@@ -53413,12 +53413,12 @@
       </c>
       <c r="AA363" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB363" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC363" t="inlineStr">
@@ -53503,7 +53503,7 @@
         </is>
       </c>
       <c r="P364" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q364" t="inlineStr">
         <is>
@@ -53557,12 +53557,12 @@
       </c>
       <c r="AA364" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB364" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC364" t="inlineStr">
@@ -53647,7 +53647,7 @@
         </is>
       </c>
       <c r="P365" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q365" t="inlineStr">
         <is>
@@ -53701,12 +53701,12 @@
       </c>
       <c r="AA365" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB365" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC365" t="inlineStr">
@@ -53791,7 +53791,7 @@
         </is>
       </c>
       <c r="P366" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q366" t="inlineStr">
         <is>
@@ -53845,12 +53845,12 @@
       </c>
       <c r="AA366" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB366" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC366" t="inlineStr">
@@ -53935,7 +53935,7 @@
         </is>
       </c>
       <c r="P367" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q367" t="inlineStr">
         <is>
@@ -53989,12 +53989,12 @@
       </c>
       <c r="AA367" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB367" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC367" t="inlineStr">
@@ -54079,7 +54079,7 @@
         </is>
       </c>
       <c r="P368" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q368" t="inlineStr">
         <is>
@@ -54133,12 +54133,12 @@
       </c>
       <c r="AA368" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB368" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC368" t="inlineStr">
@@ -54219,7 +54219,7 @@
       </c>
       <c r="O369" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P369" t="inlineStr"/>
@@ -54236,7 +54236,7 @@
       </c>
       <c r="T369" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=25-CA-005347</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=25-CA-005347</t>
         </is>
       </c>
       <c r="U369" t="inlineStr">
@@ -54246,7 +54246,7 @@
       </c>
       <c r="V369" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W369" t="inlineStr">
@@ -54271,12 +54271,12 @@
       </c>
       <c r="AA369" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB369" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC369" t="inlineStr">
